--- a/Tools/GameData.xlsx
+++ b/Tools/GameData.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Enums" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Items'!$A$1:$O$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Recipes'!$A$1:$M$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Items'!$A$1:$O$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Recipes'!$A$1:$M$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Buildings'!$A$1:$K$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Enums'!$A$1:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Enums'!$A$1:$D$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3546,12 +3546,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rope</t>
+          <t>med_kit</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>밧줄</t>
+          <t>구급낭</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
@@ -3572,29 +3572,29 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I56" t="n">
-        <v>84</v>
+        <v>206.2</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>cloth x2</t>
+          <t>med_bandage x3 + herbs x2 + alch_essence x1</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="N56" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3605,12 +3605,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>alch_essence</t>
+          <t>med_poultice</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>정제 정수</t>
+          <t>약초 습포</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
@@ -3631,29 +3631,29 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I57" t="n">
-        <v>180</v>
+        <v>193.3</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>herbs x2</t>
+          <t>herbs x3 + med_bandage x1</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N57" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3664,12 +3664,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>rope</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>밀가루</t>
+          <t>밧줄</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3678,38 +3678,38 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F58" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="J58" t="n">
         <v>1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Crop_Wheat x3</t>
+          <t>cloth x2</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="N58" t="n">
         <v>1.5</v>
@@ -3723,12 +3723,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>vegetables</t>
+          <t>med_bandage</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>채소</t>
+          <t>붕대</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -3749,10 +3749,10 @@
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I59" t="n">
-        <v>26.7</v>
+        <v>110</v>
       </c>
       <c r="J59" t="n">
         <v>1</v>
@@ -3762,9 +3762,17 @@
           <t>1x1</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>cloth x2</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>14</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1.57</v>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -3774,12 +3782,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>herbs</t>
+          <t>alch_essence</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>허브</t>
+          <t>정제 정수</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3788,10 +3796,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
@@ -3803,7 +3811,7 @@
         <v>0.1</v>
       </c>
       <c r="I60" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
@@ -3813,9 +3821,17 @@
           <t>1x1</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>herbs x2</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>12</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1.5</v>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -3825,12 +3841,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Crop_Wheat</t>
+          <t>flour</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>밀</t>
+          <t>밀가루</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3839,93 +3855,93 @@
         </is>
       </c>
       <c r="D61" t="n">
+        <v>9</v>
+      </c>
+      <c r="E61" t="n">
         <v>4</v>
       </c>
-      <c r="E61" t="n">
-        <v>2</v>
-      </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I61" t="n">
-        <v>13.3</v>
+        <v>45</v>
       </c>
       <c r="J61" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>1x1</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Crop_Wheat x3</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>6</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1.5</v>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JSON</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>arm_steel_chest</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>강철 흉갑</t>
+          <t>채소</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>몸통 방어구</t>
+          <t>잡화</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1256</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>314</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>9</v>
+        <v>0.3</v>
       </c>
       <c r="I62" t="n">
-        <v>139.6</v>
+        <v>26.7</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2x3</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Res_Steel x5 + leather x2</t>
-        </is>
-      </c>
-      <c r="M62" t="n">
-        <v>698</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1.8</v>
-      </c>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -3935,56 +3951,48 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wpn_SteelSword</t>
+          <t>herbs</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>강철 대검</t>
+          <t>허브</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>양손 검</t>
+          <t>잡화</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>992</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>273</v>
+        <v>3</v>
       </c>
       <c r="F63" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="I63" t="n">
-        <v>198.4</v>
+        <v>60</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2x4</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Res_Steel x4 + Res_Lumber x2</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>536</v>
-      </c>
-      <c r="N63" t="n">
-        <v>1.85</v>
-      </c>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -3994,55 +4002,55 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>wpn_steel_axe</t>
+          <t>med_rag</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>강철 도끼</t>
+          <t>넝마</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>양손 도끼</t>
+          <t>잡화</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>710</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>195</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="I64" t="n">
-        <v>208.8</v>
+        <v>60</v>
       </c>
       <c r="J64" t="n">
         <v>1</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2x4</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + Res_Lumber x2</t>
+          <t>cloth x1</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>406</v>
+        <v>5</v>
       </c>
       <c r="N64" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4053,83 +4061,75 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>wpn_silver_dagger</t>
+          <t>Crop_Wheat</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>은 단검</t>
+          <t>밀</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>한손 검</t>
+          <t>잡화</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>709</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>195</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="I65" t="n">
-        <v>886.2</v>
+        <v>13.3</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1x2</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Res_SilverIngot x2 + Res_Lumber x1</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
-        <v>394</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1.8</v>
-      </c>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>SO</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>arm_steel_head</t>
+          <t>arm_steel_chest</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>강철 투구</t>
+          <t>강철 흉갑</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>머리 방어구</t>
+          <t>몸통 방어구</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>704</v>
+        <v>1256</v>
       </c>
       <c r="E66" t="n">
-        <v>176</v>
+        <v>314</v>
       </c>
       <c r="F66" t="n">
         <v>4</v>
@@ -4138,29 +4138,29 @@
         <v>0.5</v>
       </c>
       <c r="H66" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="I66" t="n">
-        <v>220</v>
+        <v>139.6</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + leather x1</t>
+          <t>Res_Steel x5 + leather x2</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>414</v>
+        <v>698</v>
       </c>
       <c r="N66" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4171,83 +4171,83 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Arm_IronChest</t>
+          <t>Wpn_SteelSword</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>철 갑옷</t>
+          <t>강철 대검</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>몸통 방어구</t>
+          <t>양손 검</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>669</v>
+        <v>992</v>
       </c>
       <c r="E67" t="n">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G67" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H67" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
-        <v>83.59999999999999</v>
+        <v>198.4</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2x4</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + Res_Lumber x1</t>
+          <t>Res_Steel x4 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>398</v>
+        <v>536</v>
       </c>
       <c r="N67" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JSON</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>wpn_storm_staff</t>
+          <t>wpn_steel_axe</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>뇌전 지팡이</t>
+          <t>강철 도끼</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>지팡이</t>
+          <t>양손 도끼</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>587</v>
+        <v>710</v>
       </c>
       <c r="E68" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="F68" t="n">
         <v>3.6</v>
@@ -4256,29 +4256,29 @@
         <v>0.55</v>
       </c>
       <c r="H68" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="I68" t="n">
-        <v>279.5</v>
+        <v>208.8</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>2x4</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>crystal_elemental_lightning x1 + Res_Lumber x3</t>
+          <t>Res_Steel x3 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>309</v>
+        <v>406</v>
       </c>
       <c r="N68" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4289,24 +4289,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>wpn_flame_staff</t>
+          <t>wpn_silver_dagger</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>화염 지팡이</t>
+          <t>은 단검</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>지팡이</t>
+          <t>한손 검</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>572</v>
+        <v>709</v>
       </c>
       <c r="E69" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="F69" t="n">
         <v>3.6</v>
@@ -4315,29 +4315,29 @@
         <v>0.55</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>286</v>
+        <v>886.2</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>crystal_elemental_fire x1 + Res_Lumber x3</t>
+          <t>Res_SilverIngot x2 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>309</v>
+        <v>394</v>
       </c>
       <c r="N69" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4348,55 +4348,55 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>wpn_frost_staff</t>
+          <t>arm_steel_head</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>냉기 지팡이</t>
+          <t>강철 투구</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>지팡이</t>
+          <t>머리 방어구</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>572</v>
+        <v>704</v>
       </c>
       <c r="E70" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="F70" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="I70" t="n">
-        <v>286</v>
+        <v>220</v>
       </c>
       <c r="J70" t="n">
         <v>1</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>crystal_elemental_ice x1 + Res_Lumber x3</t>
+          <t>Res_Steel x3 + leather x1</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>309</v>
+        <v>414</v>
       </c>
       <c r="N70" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4407,83 +4407,83 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>wpn_venom_staff</t>
+          <t>Arm_IronChest</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>맹독 지팡이</t>
+          <t>철 갑옷</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>지팡이</t>
+          <t>몸통 방어구</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>557</v>
+        <v>669</v>
       </c>
       <c r="E71" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="F71" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H71" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="I71" t="n">
-        <v>309.4</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>1</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>crystal_elemental_poison x1 + Res_Lumber x2</t>
+          <t>Res_Steel x3 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>301</v>
+        <v>398</v>
       </c>
       <c r="N71" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>SO</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>wpn_steel_spear</t>
+          <t>wpn_storm_staff</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>강철 창</t>
+          <t>뇌전 지팡이</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>장병기</t>
+          <t>지팡이</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>483</v>
+        <v>587</v>
       </c>
       <c r="E72" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="F72" t="n">
         <v>3.6</v>
@@ -4492,10 +4492,10 @@
         <v>0.55</v>
       </c>
       <c r="H72" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="I72" t="n">
-        <v>185.8</v>
+        <v>279.5</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
@@ -4507,14 +4507,14 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Res_Steel x2 + Res_Lumber x3</t>
+          <t>crystal_elemental_lightning x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="N72" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -4525,24 +4525,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Wpn_BronzeSword</t>
+          <t>wpn_flame_staff</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>청동검</t>
+          <t>화염 지팡이</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>한손 검</t>
+          <t>지팡이</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>450</v>
+        <v>572</v>
       </c>
       <c r="E73" t="n">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="F73" t="n">
         <v>3.6</v>
@@ -4551,29 +4551,29 @@
         <v>0.55</v>
       </c>
       <c r="H73" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="J73" t="n">
         <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Res_Bronze x3 + Res_Lumber x1</t>
+          <t>crystal_elemental_fire x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="N73" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -4584,24 +4584,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Wpn_Crossbow</t>
+          <t>wpn_frost_staff</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>석궁</t>
+          <t>냉기 지팡이</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>쇠뇌</t>
+          <t>지팡이</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>200</v>
+        <v>572</v>
       </c>
       <c r="E74" t="n">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="F74" t="n">
         <v>3.6</v>
@@ -4610,29 +4610,29 @@
         <v>0.55</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>66.7</v>
+        <v>286</v>
       </c>
       <c r="J74" t="n">
         <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Res_Lumber x4 + Res_IronOre x2 + rope x1</t>
+          <t>crystal_elemental_ice x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>114</v>
+        <v>309</v>
       </c>
       <c r="N74" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -4643,55 +4643,55 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Arm_LeatherChest</t>
+          <t>wpn_venom_staff</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>가죽 갑옷</t>
+          <t>맹독 지팡이</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>몸통 방어구</t>
+          <t>지팡이</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>194</v>
+        <v>557</v>
       </c>
       <c r="E75" t="n">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="I75" t="n">
-        <v>64.7</v>
+        <v>309.4</v>
       </c>
       <c r="J75" t="n">
         <v>1</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>leather x5</t>
+          <t>crystal_elemental_poison x1 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>120</v>
+        <v>301</v>
       </c>
       <c r="N75" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -4702,55 +4702,55 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Arm_IronLegs</t>
+          <t>wpn_steel_spear</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>철 각반</t>
+          <t>강철 창</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>다리 방어구</t>
+          <t>장병기</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>179</v>
+        <v>483</v>
       </c>
       <c r="E76" t="n">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="F76" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H76" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="I76" t="n">
-        <v>39.8</v>
+        <v>185.8</v>
       </c>
       <c r="J76" t="n">
         <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + leather x1</t>
+          <t>Res_Steel x2 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>104</v>
+        <v>284</v>
       </c>
       <c r="N76" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -4761,24 +4761,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Wpn_IronShield</t>
+          <t>Wpn_BronzeSword</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>철 방패</t>
+          <t>청동검</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>방패</t>
+          <t>한손 검</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>163</v>
+        <v>450</v>
       </c>
       <c r="E77" t="n">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="F77" t="n">
         <v>3.6</v>
@@ -4787,29 +4787,29 @@
         <v>0.55</v>
       </c>
       <c r="H77" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I77" t="n">
-        <v>108.7</v>
+        <v>180</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x2</t>
+          <t>Res_Bronze x3 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>96</v>
+        <v>281</v>
       </c>
       <c r="N77" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -4820,55 +4820,55 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wpn_IronMace</t>
+          <t>Wpn_Crossbow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>철 철퇴</t>
+          <t>석궁</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>한손 둔기</t>
+          <t>쇠뇌</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E78" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F78" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G78" t="n">
         <v>0.55</v>
       </c>
       <c r="H78" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I78" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="J78" t="n">
         <v>1</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x1</t>
+          <t>Res_Lumber x4 + Res_IronOre x2 + rope x1</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="N78" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -4879,83 +4879,83 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Wpn_IronSword</t>
+          <t>Arm_LeatherChest</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>철검</t>
+          <t>가죽 갑옷</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>한손 검</t>
+          <t>몸통 방어구</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="E79" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F79" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G79" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H79" t="n">
         <v>3</v>
       </c>
       <c r="I79" t="n">
-        <v>48</v>
+        <v>64.7</v>
       </c>
       <c r="J79" t="n">
         <v>1</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x1</t>
+          <t>leather x5</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="N79" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JSON</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Arm_IronHands</t>
+          <t>Arm_IronLegs</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>철 건틀릿</t>
+          <t>철 각반</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>손 방어구</t>
+          <t>다리 방어구</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="E80" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F80" t="n">
         <v>4</v>
@@ -4964,29 +4964,29 @@
         <v>0.5</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="I80" t="n">
-        <v>71.5</v>
+        <v>39.8</v>
       </c>
       <c r="J80" t="n">
         <v>1</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Res_IronOre x3 + leather x1</t>
+          <t>Res_IronOre x4 + leather x1</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="N80" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -4997,52 +4997,52 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Wpn_IronAxe</t>
+          <t>Wpn_IronShield</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>철도끼</t>
+          <t>철 방패</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>한손 도끼</t>
+          <t>방패</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="E81" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F81" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G81" t="n">
         <v>0.55</v>
       </c>
       <c r="H81" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="I81" t="n">
-        <v>36.9</v>
+        <v>108.7</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Res_IronOre x3 + Res_Lumber x2</t>
+          <t>Res_IronOre x4 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="N81" t="n">
         <v>1.7</v>
@@ -5056,55 +5056,55 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>wpn_longbow</t>
+          <t>Wpn_IronMace</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>장궁</t>
+          <t>철 철퇴</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>활</t>
+          <t>한손 둔기</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="E82" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F82" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G82" t="n">
         <v>0.55</v>
       </c>
       <c r="H82" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="I82" t="n">
-        <v>76.2</v>
+        <v>42.9</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Res_Lumber x4 + rope x1</t>
+          <t>Res_IronOre x4 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="N82" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5115,114 +5115,114 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Wpn_Spear</t>
+          <t>Wpn_IronSword</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>장창</t>
+          <t>철검</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>장병기</t>
+          <t>한손 검</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="E83" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F83" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G83" t="n">
         <v>0.55</v>
       </c>
       <c r="H83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I83" t="n">
-        <v>29.5</v>
+        <v>48</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Res_IronOre x2 + Res_Lumber x4</t>
+          <t>Res_IronOre x4 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="N83" t="n">
         <v>1.64</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>SO</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Arm_LeatherLegs</t>
+          <t>Arm_IronHands</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>가죽 각반</t>
+          <t>철 건틀릿</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>다리 방어구</t>
+          <t>손 방어구</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="E84" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F84" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G84" t="n">
         <v>0.5</v>
       </c>
       <c r="H84" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
-        <v>71.2</v>
+        <v>71.5</v>
       </c>
       <c r="J84" t="n">
         <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>leather x3</t>
+          <t>Res_IronOre x3 + leather x1</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="N84" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5233,24 +5233,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Wpn_ShortBow</t>
+          <t>Wpn_IronAxe</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>단궁</t>
+          <t>철도끼</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>활</t>
+          <t>한손 도끼</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="E85" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F85" t="n">
         <v>3.7</v>
@@ -5259,29 +5259,29 @@
         <v>0.55</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="I85" t="n">
-        <v>53</v>
+        <v>36.9</v>
       </c>
       <c r="J85" t="n">
         <v>1</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Res_Lumber x3 + rope x1</t>
+          <t>Res_IronOre x3 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="N85" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -5292,55 +5292,55 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Arm_IronHead</t>
+          <t>wpn_longbow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>철 투구</t>
+          <t>장궁</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>머리 방어구</t>
+          <t>활</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="E86" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F86" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="G86" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H86" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="I86" t="n">
-        <v>34</v>
+        <v>76.2</v>
       </c>
       <c r="J86" t="n">
         <v>1</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Res_IronOre x3</t>
+          <t>Res_Lumber x4 + rope x1</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="N86" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -5351,55 +5351,55 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>arm_cloth_chest</t>
+          <t>Wpn_Spear</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>천 옷</t>
+          <t>장창</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>몸통 방어구</t>
+          <t>장병기</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="E87" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F87" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H87" t="n">
         <v>4</v>
       </c>
-      <c r="G87" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0.8</v>
-      </c>
       <c r="I87" t="n">
-        <v>105</v>
+        <v>29.5</v>
       </c>
       <c r="J87" t="n">
         <v>1</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>cloth x4</t>
+          <t>Res_IronOre x2 + Res_Lumber x4</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="N87" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -5410,24 +5410,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Arm_LeatherHands</t>
+          <t>Arm_LeatherLegs</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>가죽 장갑</t>
+          <t>가죽 각반</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>손 방어구</t>
+          <t>다리 방어구</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="E88" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F88" t="n">
         <v>4.1</v>
@@ -5436,29 +5436,29 @@
         <v>0.5</v>
       </c>
       <c r="H88" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="I88" t="n">
-        <v>92.5</v>
+        <v>71.2</v>
       </c>
       <c r="J88" t="n">
         <v>1</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>leather x2</t>
+          <t>leather x3</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="N88" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -5469,55 +5469,55 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Arm_LeatherHead</t>
+          <t>Wpn_ShortBow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>가죽 모자</t>
+          <t>단궁</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>머리 방어구</t>
+          <t>활</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="E89" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="G89" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H89" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
-        <v>61.7</v>
+        <v>53</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>leather x2</t>
+          <t>Res_Lumber x3 + rope x1</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="N89" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -5528,70 +5528,306 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>Arm_IronHead</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>철 투구</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>머리 방어구</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>102</v>
+      </c>
+      <c r="E90" t="n">
+        <v>26</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I90" t="n">
+        <v>34</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Res_IronOre x3</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>60</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>arm_cloth_chest</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>천 옷</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>몸통 방어구</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>84</v>
+      </c>
+      <c r="E91" t="n">
+        <v>21</v>
+      </c>
+      <c r="F91" t="n">
+        <v>4</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I91" t="n">
+        <v>105</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2x3</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>cloth x4</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>56</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Arm_LeatherHands</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>가죽 장갑</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>손 방어구</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>74</v>
+      </c>
+      <c r="E92" t="n">
+        <v>18</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I92" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>leather x2</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>48</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Arm_LeatherHead</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>가죽 모자</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>머리 방어구</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>74</v>
+      </c>
+      <c r="E93" t="n">
+        <v>18</v>
+      </c>
+      <c r="F93" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I93" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>leather x2</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>48</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>Wpn_WoodShield</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>나무 방패</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>방패</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D94" t="n">
         <v>50</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E94" t="n">
         <v>14</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F94" t="n">
         <v>3.6</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G94" t="n">
         <v>0.55</v>
       </c>
-      <c r="H90" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" t="n">
+      <c r="H94" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" t="n">
         <v>50</v>
       </c>
-      <c r="J90" t="n">
-        <v>1</v>
-      </c>
-      <c r="K90" t="inlineStr">
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>2x2</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>Res_Lumber x4</t>
         </is>
       </c>
-      <c r="M90" t="n">
+      <c r="M94" t="n">
         <v>32</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N94" t="n">
         <v>1.56</v>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O90"/>
-  <conditionalFormatting sqref="N2:N90">
+  <autoFilter ref="A1:O94"/>
+  <conditionalFormatting sqref="N2:N94">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D90">
+  <conditionalFormatting sqref="D2:D94">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5611,7 +5847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5754,17 +5990,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alch_potion_stamina</t>
+          <t>alch_medkit</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>활력 물약 조제</t>
+          <t>구급낭 꾸리기</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>potion_stamina</t>
+          <t>med_kit</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -5772,17 +6008,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>alch_essence x1 + vegetables x2</t>
+          <t>med_bandage x3 + herbs x2 + alch_essence x1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="G3" t="n">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -5793,13 +6029,9 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Res_Alchemy</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -5809,17 +6041,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>alch_potion_heal</t>
+          <t>alch_potion_stamina</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>치유 물약 조제</t>
+          <t>활력 물약 조제</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>potion_heal</t>
+          <t>potion_stamina</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -5827,17 +6059,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>alch_essence x2 + herbs x1</t>
+          <t>alch_essence x1 + vegetables x2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H4" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -5845,10 +6077,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -5864,35 +6096,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>alch_potion_antidote</t>
+          <t>alch_poultice</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>해독제 조제</t>
+          <t>약초 습포</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>potion_antidote</t>
+          <t>med_poultice</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>alch_essence x2 + herbs x3</t>
+          <t>herbs x3 + med_bandage x1</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -5900,16 +6132,12 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Res_Alchemy</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -5919,17 +6147,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>craft_iron_hands</t>
+          <t>alch_potion_heal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>철 건틀릿 제작</t>
+          <t>치유 물약 조제</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arm_IronHands</t>
+          <t>potion_heal</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -5937,32 +6165,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Res_IronOre x3 + leather x1</t>
+          <t>alch_essence x2 + herbs x1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ArmorCrafting</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Res_WeaponSmithing</t>
+          <t>Res_Alchemy</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5974,17 +6202,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>craft_iron_head</t>
+          <t>alch_potion_antidote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>철 투구 제작</t>
+          <t>해독제 조제</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arm_IronHead</t>
+          <t>potion_antidote</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -5992,32 +6220,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Res_IronOre x3</t>
+          <t>alch_essence x2 + herbs x3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ArmorCrafting</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Res_WeaponSmithing</t>
+          <t>Res_Alchemy</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -6029,17 +6257,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>craft_iron_shield</t>
+          <t>craft_cloth_chest</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>철 방패 제작</t>
+          <t>천 옷 제작</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wpn_IronShield</t>
+          <t>arm_cloth_chest</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -6047,17 +6275,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x2</t>
+          <t>cloth x4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -6065,16 +6293,12 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Res_WeaponSmithing</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6084,17 +6308,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>craft_steel_head</t>
+          <t>craft_leather_hands</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>강철 투구 제작</t>
+          <t>가죽 장갑 제작</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>arm_steel_head</t>
+          <t>Arm_LeatherHands</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -6102,17 +6326,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + leather x1</t>
+          <t>leather x2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>414</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>704</v>
+        <v>74</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -6120,16 +6344,12 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Res_Steelmaking</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6139,17 +6359,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>craft_iron_legs</t>
+          <t>craft_leather_head</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>철 각반 제작</t>
+          <t>가죽 모자 제작</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Arm_IronLegs</t>
+          <t>Arm_LeatherHead</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -6157,17 +6377,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + leather x1</t>
+          <t>leather x2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="H10" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -6175,16 +6395,12 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Res_WeaponSmithing</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6194,17 +6410,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>craft_steel_chest</t>
+          <t>craft_leather_legs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>강철 흉갑 제작</t>
+          <t>가죽 각반 제작</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>arm_steel_chest</t>
+          <t>Arm_LeatherLegs</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -6212,17 +6428,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Res_Steel x5 + leather x2</t>
+          <t>leather x3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>698</v>
+        <v>72</v>
       </c>
       <c r="G11" t="n">
-        <v>1256</v>
+        <v>114</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -6230,16 +6446,12 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>22</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Res_Steelmaking</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6249,52 +6461,48 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cook_dried_meat</t>
+          <t>craft_leather_chest</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>고기 말리기</t>
+          <t>가죽 갑옷 제작</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>food_dried_meat</t>
+          <t>Arm_LeatherChest</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Food_RawMeat x2</t>
+          <t>leather x5</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>120</v>
+      </c>
+      <c r="G12" t="n">
+        <v>194</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ArmorCrafting</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" t="n">
         <v>16</v>
       </c>
-      <c r="G12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Cooking</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Res_Cooking</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6304,48 +6512,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cook_flour</t>
+          <t>craft_iron_hands</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>밀가루 빻기</t>
+          <t>철 건틀릿 제작</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>Arm_IronHands</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Crop_Wheat x3</t>
+          <t>Res_IronOre x3 + leather x1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>ArmorCrafting</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Res_WeaponSmithing</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6355,50 +6567,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cook_herbal_tea</t>
+          <t>craft_iron_head</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>허브차 만들기</t>
+          <t>철 투구 제작</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>food_herbal_tea</t>
+          <t>Arm_IronHead</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>herbs x2</t>
+          <t>Res_IronOre x3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>ArmorCrafting</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Res_Cooking</t>
+          <t>Res_WeaponSmithing</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6410,17 +6622,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cook_vegetable_soup</t>
+          <t>craft_iron_shield</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>채소 수프 끓이기</t>
+          <t>철 방패 제작</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>food_vegetable_soup</t>
+          <t>Wpn_IronShield</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -6428,32 +6640,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>vegetables x2</t>
+          <t>Res_IronOre x4 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="G15" t="n">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>ArmorCrafting</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Res_Cooking</t>
+          <t>Res_WeaponSmithing</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6465,17 +6677,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cook_cheese</t>
+          <t>craft_steel_head</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>치즈 만들기</t>
+          <t>강철 투구 제작</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>food_cheese</t>
+          <t>arm_steel_head</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -6483,32 +6695,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>vegetables x2 + herbs x1</t>
+          <t>Res_Steel x3 + leather x1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>414</v>
       </c>
       <c r="G16" t="n">
-        <v>36</v>
+        <v>704</v>
       </c>
       <c r="H16" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>ArmorCrafting</t>
         </is>
       </c>
       <c r="J16" t="n">
+        <v>20</v>
+      </c>
+      <c r="K16" t="n">
         <v>15</v>
       </c>
-      <c r="K16" t="n">
-        <v>10</v>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Res_Cooking</t>
+          <t>Res_Steelmaking</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6520,17 +6732,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cook_stew</t>
+          <t>craft_iron_legs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>스튜 끓이기</t>
+          <t>철 각반 제작</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>food_stew</t>
+          <t>Arm_IronLegs</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -6538,32 +6750,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Food_RawMeat x1 + vegetables x2</t>
+          <t>Res_IronOre x4 + leather x1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="G17" t="n">
-        <v>40</v>
+        <v>179</v>
       </c>
       <c r="H17" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>ArmorCrafting</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Res_Cooking</t>
+          <t>Res_WeaponSmithing</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -6575,17 +6787,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cook_feast</t>
+          <t>craft_steel_chest</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>진수성찬 준비</t>
+          <t>강철 흉갑 제작</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>food_feast</t>
+          <t>arm_steel_chest</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -6593,32 +6805,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Food_CookedMeat x2 + vegetables x2 + Food_Bread x2</t>
+          <t>Res_Steel x5 + leather x2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>698</v>
       </c>
       <c r="G18" t="n">
-        <v>110</v>
+        <v>1256</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>ArmorCrafting</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Res_Cooking</t>
+          <t>Res_Steelmaking</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -6630,48 +6842,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gem_elemental_fire</t>
+          <t>cook_dried_meat</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>원소 화염 결정 제작</t>
+          <t>고기 말리기</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>crystal_elemental_fire</t>
+          <t>food_dried_meat</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Res_Ruby x1 + Res_MagicStone x1</t>
+          <t>Food_RawMeat x2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>190</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="H19" t="n">
         <v>1.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Cooking</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Res_Cooking</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6681,46 +6897,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gem_elemental_ice</t>
+          <t>cook_flour</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>원소 냉기 결정 제작</t>
+          <t>밀가루 빻기</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>crystal_elemental_ice</t>
+          <t>flour</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Res_Sapphire x1 + Res_MagicStone x1</t>
+          <t>Crop_Wheat x3</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>190</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>285</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
         <v>1.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Cooking</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
@@ -6732,48 +6948,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gem_elemental_lightning</t>
+          <t>cook_herbal_tea</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>원소 번개 결정 제작</t>
+          <t>허브차 만들기</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>crystal_elemental_lightning</t>
+          <t>food_herbal_tea</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Res_Topaz x1 + Res_MagicStone x1</t>
+          <t>herbs x2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>190</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
-        <v>285</v>
+        <v>18</v>
       </c>
       <c r="H21" t="n">
         <v>1.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Cooking</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Res_Cooking</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6783,17 +7003,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gem_elemental_poison</t>
+          <t>cook_vegetable_soup</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>원소 독 결정 제작</t>
+          <t>채소 수프 끓이기</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>crystal_elemental_poison</t>
+          <t>food_vegetable_soup</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -6801,30 +7021,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Res_Emerald x1 + Res_MagicStone x1</t>
+          <t>vegetables x2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>190</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="H22" t="n">
         <v>1.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Cooking</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Res_Cooking</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6834,17 +7058,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gem_dark_fire</t>
+          <t>cook_cheese</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>암흑 화염 결정 제작</t>
+          <t>치즈 만들기</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>crystal_dark_fire</t>
+          <t>food_cheese</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -6852,30 +7076,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Res_Ruby x1 + Res_Voidstone x1</t>
+          <t>vegetables x2 + herbs x1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
-        <v>357</v>
+        <v>36</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Cooking</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>12</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Res_Cooking</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6885,17 +7113,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gem_dark_ice</t>
+          <t>cook_stew</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>암흑 냉기 결정 제작</t>
+          <t>스튜 끓이기</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>crystal_dark_ice</t>
+          <t>food_stew</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -6903,30 +7131,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Res_Sapphire x1 + Res_Voidstone x1</t>
+          <t>Food_RawMeat x1 + vegetables x2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>210</v>
+        <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>357</v>
+        <v>40</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Cooking</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
         <v>12</v>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Res_Cooking</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6936,17 +7168,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gem_dark_lightning</t>
+          <t>cook_feast</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>암흑 번개 결정 제작</t>
+          <t>진수성찬 준비</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>crystal_dark_lightning</t>
+          <t>food_feast</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -6954,30 +7186,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Res_Topaz x1 + Res_Voidstone x1</t>
+          <t>Food_CookedMeat x2 + vegetables x2 + Food_Bread x2</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="G25" t="n">
-        <v>357</v>
+        <v>110</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Cooking</t>
         </is>
       </c>
       <c r="J25" t="n">
+        <v>40</v>
+      </c>
+      <c r="K25" t="n">
         <v>20</v>
       </c>
-      <c r="K25" t="n">
-        <v>12</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Res_Cooking</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -6987,17 +7223,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gem_dark_poison</t>
+          <t>gem_elemental_fire</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>암흑 독 결정 제작</t>
+          <t>원소 화염 결정 제작</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>crystal_dark_poison</t>
+          <t>crystal_elemental_fire</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -7005,17 +7241,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Res_Emerald x1 + Res_Voidstone x1</t>
+          <t>Res_Ruby x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G26" t="n">
-        <v>357</v>
+        <v>285</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -7023,10 +7259,10 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
@@ -7038,17 +7274,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gem_holy_fire</t>
+          <t>gem_elemental_ice</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>신성 화염 결정 제작</t>
+          <t>원소 냉기 결정 제작</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>crystal_holy_fire</t>
+          <t>crystal_elemental_ice</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -7056,17 +7292,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Res_Ruby x1 + Res_Etherstone x1</t>
+          <t>Res_Sapphire x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G27" t="n">
-        <v>357</v>
+        <v>285</v>
       </c>
       <c r="H27" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -7074,10 +7310,10 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
@@ -7089,17 +7325,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gem_holy_ice</t>
+          <t>gem_elemental_lightning</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>신성 냉기 결정 제작</t>
+          <t>원소 번개 결정 제작</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>crystal_holy_ice</t>
+          <t>crystal_elemental_lightning</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -7107,17 +7343,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Res_Sapphire x1 + Res_Etherstone x1</t>
+          <t>Res_Topaz x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G28" t="n">
-        <v>357</v>
+        <v>285</v>
       </c>
       <c r="H28" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -7125,10 +7361,10 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
@@ -7140,17 +7376,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gem_holy_lightning</t>
+          <t>gem_elemental_poison</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>신성 번개 결정 제작</t>
+          <t>원소 독 결정 제작</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>crystal_holy_lightning</t>
+          <t>crystal_elemental_poison</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -7158,17 +7394,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Res_Topaz x1 + Res_Etherstone x1</t>
+          <t>Res_Emerald x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G29" t="n">
-        <v>357</v>
+        <v>285</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -7176,10 +7412,10 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
@@ -7191,17 +7427,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gem_holy_poison</t>
+          <t>gem_dark_fire</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>신성 독 결정 제작</t>
+          <t>암흑 화염 결정 제작</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>crystal_holy_poison</t>
+          <t>crystal_dark_fire</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -7209,7 +7445,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Res_Emerald x1 + Res_Etherstone x1</t>
+          <t>Res_Ruby x1 + Res_Voidstone x1</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -7242,46 +7478,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>craft_cloth</t>
+          <t>gem_dark_ice</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>천 짜기</t>
+          <t>암흑 냉기 결정 제작</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>cloth</t>
+          <t>crystal_dark_ice</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>herbs x3</t>
+          <t>Res_Sapphire x1 + Res_Voidstone x1</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="G31" t="n">
-        <v>28</v>
+        <v>357</v>
       </c>
       <c r="H31" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Gemcutting</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
@@ -7293,17 +7529,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>craft_cloth_chest</t>
+          <t>gem_dark_lightning</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>천 옷 제작</t>
+          <t>암흑 번개 결정 제작</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>arm_cloth_chest</t>
+          <t>crystal_dark_lightning</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -7311,28 +7547,28 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>cloth x4</t>
+          <t>Res_Topaz x1 + Res_Voidstone x1</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="G32" t="n">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Gemcutting</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
@@ -7344,17 +7580,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>craft_leather</t>
+          <t>gem_dark_poison</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>가죽 무두질</t>
+          <t>암흑 독 결정 제작</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>crystal_dark_poison</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -7362,28 +7598,28 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Food_RawMeat x2</t>
+          <t>Res_Emerald x1 + Res_Voidstone x1</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="G33" t="n">
-        <v>24</v>
+        <v>357</v>
       </c>
       <c r="H33" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Gemcutting</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
@@ -7395,17 +7631,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>craft_rope</t>
+          <t>gem_holy_fire</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>밧줄 꼬기</t>
+          <t>신성 화염 결정 제작</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>rope</t>
+          <t>crystal_holy_fire</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -7413,28 +7649,28 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>cloth x2</t>
+          <t>Res_Ruby x1 + Res_Etherstone x1</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="G34" t="n">
-        <v>42</v>
+        <v>357</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Gemcutting</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
@@ -7446,17 +7682,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>craft_leather_hands</t>
+          <t>gem_holy_ice</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>가죽 장갑 제작</t>
+          <t>신성 냉기 결정 제작</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arm_LeatherHands</t>
+          <t>crystal_holy_ice</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -7464,28 +7700,28 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>leather x2</t>
+          <t>Res_Sapphire x1 + Res_Etherstone x1</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="G35" t="n">
-        <v>74</v>
+        <v>357</v>
       </c>
       <c r="H35" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Gemcutting</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
@@ -7497,17 +7733,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>craft_leather_head</t>
+          <t>gem_holy_lightning</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>가죽 모자 제작</t>
+          <t>신성 번개 결정 제작</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arm_LeatherHead</t>
+          <t>crystal_holy_lightning</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -7515,28 +7751,28 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>leather x2</t>
+          <t>Res_Topaz x1 + Res_Etherstone x1</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="G36" t="n">
-        <v>74</v>
+        <v>357</v>
       </c>
       <c r="H36" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Gemcutting</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
@@ -7548,17 +7784,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>craft_wood_shield</t>
+          <t>gem_holy_poison</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>나무 방패 제작</t>
+          <t>신성 독 결정 제작</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wpn_WoodShield</t>
+          <t>crystal_holy_poison</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -7566,28 +7802,28 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Res_Lumber x4</t>
+          <t>Res_Emerald x1 + Res_Etherstone x1</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>32</v>
+        <v>210</v>
       </c>
       <c r="G37" t="n">
-        <v>50</v>
+        <v>357</v>
       </c>
       <c r="H37" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Gemcutting</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
@@ -7599,35 +7835,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>craft_leather_legs</t>
+          <t>craft_bandage</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>가죽 각반 제작</t>
+          <t>붕대 만들기</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arm_LeatherLegs</t>
+          <t>med_bandage</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>leather x3</t>
+          <t>cloth x2</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="G38" t="n">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="H38" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -7635,10 +7871,10 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
@@ -7650,35 +7886,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>craft_short_bow</t>
+          <t>craft_cloth</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>단궁 제작</t>
+          <t>천 짜기</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wpn_ShortBow</t>
+          <t>cloth</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Res_Lumber x3 + rope x1</t>
+          <t>herbs x3</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="G39" t="n">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="H39" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -7686,10 +7922,10 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
@@ -7701,17 +7937,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>craft_leather_chest</t>
+          <t>craft_leather</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>가죽 갑옷 제작</t>
+          <t>가죽 무두질</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arm_LeatherChest</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7719,17 +7955,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>leather x5</t>
+          <t>Food_RawMeat x2</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="G40" t="n">
-        <v>194</v>
+        <v>24</v>
       </c>
       <c r="H40" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -7737,10 +7973,10 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
@@ -7752,35 +7988,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>craft_longbow</t>
+          <t>craft_rag</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>장궁 제작</t>
+          <t>넝마 찢기</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>wpn_longbow</t>
+          <t>med_rag</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Res_Lumber x4 + rope x1</t>
+          <t>cloth x1</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="G41" t="n">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="H41" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -7788,16 +8024,12 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>13</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Res_WeaponSmithing</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -7807,17 +8039,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>craft_bronze_sword</t>
+          <t>craft_rope</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>청동검 제작</t>
+          <t>밧줄 꼬기</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wpn_BronzeSword</t>
+          <t>rope</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -7825,34 +8057,30 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Res_Bronze x3 + Res_Lumber x1</t>
+          <t>cloth x2</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>281</v>
+        <v>28</v>
       </c>
       <c r="G42" t="n">
-        <v>450</v>
+        <v>42</v>
       </c>
       <c r="H42" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>WeaponCrafting</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>12</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Res_Smelting</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -7862,17 +8090,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>craft_spear</t>
+          <t>craft_wood_shield</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>장창 제작</t>
+          <t>나무 방패 제작</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wpn_Spear</t>
+          <t>Wpn_WoodShield</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -7880,28 +8108,28 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Res_IronOre x2 + Res_Lumber x4</t>
+          <t>Res_Lumber x4</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="G43" t="n">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="H43" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>WeaponCrafting</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
@@ -7913,17 +8141,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>craft_iron_axe</t>
+          <t>craft_short_bow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>철도끼 제작</t>
+          <t>단궁 제작</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wpn_IronAxe</t>
+          <t>Wpn_ShortBow</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -7931,34 +8159,30 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Res_IronOre x3 + Res_Lumber x2</t>
+          <t>Res_Lumber x3 + rope x1</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="G44" t="n">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="H44" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>WeaponCrafting</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>14</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Res_WeaponSmithing</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -7968,17 +8192,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>craft_iron_mace</t>
+          <t>craft_longbow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>철 철퇴 제작</t>
+          <t>장궁 제작</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wpn_IronMace</t>
+          <t>wpn_longbow</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -7986,28 +8210,28 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x1</t>
+          <t>Res_Lumber x4 + rope x1</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G45" t="n">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="H45" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>WeaponCrafting</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K45" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -8023,17 +8247,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>craft_steel_spear</t>
+          <t>craft_bronze_sword</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>강철 창 제작</t>
+          <t>청동검 제작</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>wpn_steel_spear</t>
+          <t>Wpn_BronzeSword</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -8041,17 +8265,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Res_Steel x2 + Res_Lumber x3</t>
+          <t>Res_Bronze x3 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G46" t="n">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="H46" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -8059,14 +8283,14 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Res_WeaponSmithing</t>
+          <t>Res_Smelting</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -8078,17 +8302,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>craft_crossbow</t>
+          <t>craft_spear</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>석궁 제작</t>
+          <t>장창 제작</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wpn_Crossbow</t>
+          <t>Wpn_Spear</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -8096,17 +8320,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Res_Lumber x4 + Res_IronOre x2 + rope x1</t>
+          <t>Res_IronOre x2 + Res_Lumber x4</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="G47" t="n">
-        <v>200</v>
+        <v>118</v>
       </c>
       <c r="H47" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -8114,16 +8338,12 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
-        <v>18</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Res_WeaponSmithing</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -8133,17 +8353,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>craft_steel_axe</t>
+          <t>craft_iron_axe</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>강철 도끼 제작</t>
+          <t>철도끼 제작</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>wpn_steel_axe</t>
+          <t>Wpn_IronAxe</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -8151,17 +8371,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + Res_Lumber x2</t>
+          <t>Res_IronOre x3 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>406</v>
+        <v>76</v>
       </c>
       <c r="G48" t="n">
-        <v>710</v>
+        <v>129</v>
       </c>
       <c r="H48" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -8169,10 +8389,10 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -8188,17 +8408,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>craft_silver_dagger</t>
+          <t>craft_iron_mace</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>은 단검 제작</t>
+          <t>철 철퇴 제작</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>wpn_silver_dagger</t>
+          <t>Wpn_IronMace</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -8206,17 +8426,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Res_SilverIngot x2 + Res_Lumber x1</t>
+          <t>Res_IronOre x4 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>394</v>
+        <v>88</v>
       </c>
       <c r="G49" t="n">
-        <v>709</v>
+        <v>150</v>
       </c>
       <c r="H49" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -8224,10 +8444,10 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -8243,17 +8463,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>craft_flame_staff</t>
+          <t>craft_steel_spear</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>화염 지팡이 제작</t>
+          <t>강철 창 제작</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>wpn_flame_staff</t>
+          <t>wpn_steel_spear</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -8261,17 +8481,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>crystal_elemental_fire x1 + Res_Lumber x3</t>
+          <t>Res_Steel x2 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="G50" t="n">
-        <v>572</v>
+        <v>483</v>
       </c>
       <c r="H50" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -8279,14 +8499,14 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Res_ElementalCraft</t>
+          <t>Res_WeaponSmithing</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -8298,17 +8518,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>craft_frost_staff</t>
+          <t>craft_crossbow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>냉기 지팡이 제작</t>
+          <t>석궁 제작</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>wpn_frost_staff</t>
+          <t>Wpn_Crossbow</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -8316,17 +8536,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>crystal_elemental_ice x1 + Res_Lumber x3</t>
+          <t>Res_Lumber x4 + Res_IronOre x2 + rope x1</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>309</v>
+        <v>114</v>
       </c>
       <c r="G51" t="n">
-        <v>572</v>
+        <v>200</v>
       </c>
       <c r="H51" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -8334,14 +8554,14 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Res_ElementalCraft</t>
+          <t>Res_WeaponSmithing</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -8353,17 +8573,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>craft_steel_sword</t>
+          <t>craft_steel_axe</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>강철 대검 제작</t>
+          <t>강철 도끼 제작</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wpn_SteelSword</t>
+          <t>wpn_steel_axe</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -8371,17 +8591,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Res_Steel x4 + Res_Lumber x2</t>
+          <t>Res_Steel x3 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>536</v>
+        <v>406</v>
       </c>
       <c r="G52" t="n">
-        <v>992</v>
+        <v>710</v>
       </c>
       <c r="H52" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -8389,14 +8609,14 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Res_Steelmaking</t>
+          <t>Res_WeaponSmithing</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -8408,17 +8628,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>craft_venom_staff</t>
+          <t>craft_silver_dagger</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>맹독 지팡이 제작</t>
+          <t>은 단검 제작</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>wpn_venom_staff</t>
+          <t>wpn_silver_dagger</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -8426,17 +8646,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>crystal_elemental_poison x1 + Res_Lumber x2</t>
+          <t>Res_SilverIngot x2 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>301</v>
+        <v>394</v>
       </c>
       <c r="G53" t="n">
-        <v>557</v>
+        <v>709</v>
       </c>
       <c r="H53" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -8444,14 +8664,14 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K53" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Res_ElementalCraft</t>
+          <t>Res_WeaponSmithing</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -8463,17 +8683,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>craft_storm_staff</t>
+          <t>craft_flame_staff</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>뇌전 지팡이 제작</t>
+          <t>화염 지팡이 제작</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>wpn_storm_staff</t>
+          <t>wpn_flame_staff</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -8481,17 +8701,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>crystal_elemental_lightning x1 + Res_Lumber x3</t>
+          <t>crystal_elemental_fire x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>309</v>
       </c>
       <c r="G54" t="n">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="H54" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -8499,10 +8719,10 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K54" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -8518,68 +8738,72 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Rec_Lumber</t>
+          <t>craft_frost_staff</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>판자</t>
+          <t>냉기 지팡이 제작</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Res_Lumber</t>
+          <t>wpn_frost_staff</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Res_Wood x3</t>
+          <t>crystal_elemental_ice x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>9</v>
+        <v>309</v>
       </c>
       <c r="G55" t="n">
-        <v>16</v>
+        <v>572</v>
       </c>
       <c r="H55" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>목공</t>
+          <t>WeaponCrafting</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="K55" t="n">
-        <v>12</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Res_ElementalCraft</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JSON</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Rec_IronSword</t>
+          <t>craft_steel_sword</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>철검</t>
+          <t>강철 대검 제작</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wpn_IronSword</t>
+          <t>Wpn_SteelSword</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -8587,50 +8811,54 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x1</t>
+          <t>Res_Steel x4 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>88</v>
+        <v>536</v>
       </c>
       <c r="G56" t="n">
-        <v>144</v>
+        <v>992</v>
       </c>
       <c r="H56" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>무기제작</t>
+          <t>WeaponCrafting</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>90</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Res_Steelmaking</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JSON</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rec_IronChest</t>
+          <t>craft_venom_staff</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>철 갑옷</t>
+          <t>맹독 지팡이 제작</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Arm_IronChest</t>
+          <t>wpn_venom_staff</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -8638,50 +8866,54 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + Res_Lumber x1</t>
+          <t>crystal_elemental_poison x1 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="G57" t="n">
-        <v>669</v>
+        <v>557</v>
       </c>
       <c r="H57" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>방어구제작</t>
+          <t>WeaponCrafting</t>
         </is>
       </c>
       <c r="J57" t="n">
+        <v>35</v>
+      </c>
+      <c r="K57" t="n">
         <v>18</v>
       </c>
-      <c r="K57" t="n">
-        <v>120</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Res_ElementalCraft</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JSON</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rec_CutStone</t>
+          <t>craft_storm_staff</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>다듬은 돌</t>
+          <t>뇌전 지팡이 제작</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Res_CutStone</t>
+          <t>wpn_storm_staff</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -8689,50 +8921,54 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Res_Stone x2</t>
+          <t>crystal_elemental_lightning x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>309</v>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>587</v>
       </c>
       <c r="H58" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>석공</t>
+          <t>WeaponCrafting</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="K58" t="n">
-        <v>15</v>
-      </c>
-      <c r="L58" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Res_ElementalCraft</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JSON</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Rec_Bread</t>
+          <t>Rec_Lumber</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>빵</t>
+          <t>판자</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Food_Bread</t>
+          <t>Res_Lumber</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -8740,28 +8976,28 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crop_Wheat x3</t>
+          <t>Res_Wood x3</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G59" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H59" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>요리</t>
+          <t>목공</t>
         </is>
       </c>
       <c r="J59" t="n">
         <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
@@ -8773,17 +9009,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Rec_CookedMeat</t>
+          <t>Rec_IronSword</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>구운 고기</t>
+          <t>철검</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Food_CookedMeat</t>
+          <t>Wpn_IronSword</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -8791,28 +9027,28 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Food_RawMeat x1</t>
+          <t>Res_IronOre x4 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="G60" t="n">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="H60" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>요리</t>
+          <t>무기제작</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K60" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
@@ -8824,17 +9060,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Rec_Bronze</t>
+          <t>Rec_IronChest</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>청동 주괴</t>
+          <t>철 갑옷</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Res_Bronze</t>
+          <t>Arm_IronChest</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -8842,28 +9078,28 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Res_CopperOre x3 + Res_TinOre x1 + Res_Coal x1</t>
+          <t>Res_Steel x3 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>60</v>
+        <v>398</v>
       </c>
       <c r="G61" t="n">
-        <v>91</v>
+        <v>669</v>
       </c>
       <c r="H61" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>제련</t>
+          <t>방어구제작</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K61" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
@@ -8875,17 +9111,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Rec_Steel</t>
+          <t>Rec_CutStone</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>강철 주괴</t>
+          <t>다듬은 돌</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Res_Steel</t>
+          <t>Res_CutStone</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -8893,28 +9129,28 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Res_IronOre x3 + Res_Coal x2</t>
+          <t>Res_Stone x2</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="G62" t="n">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="H62" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>제련</t>
+          <t>석공</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
@@ -8926,46 +9162,46 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rec_SilverIngot</t>
+          <t>Rec_Bread</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>은 주괴</t>
+          <t>빵</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Res_SilverIngot</t>
+          <t>Food_Bread</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Res_SilverOre x3 + Res_Coal x1</t>
+          <t>Crop_Wheat x3</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>115</v>
+        <v>12</v>
       </c>
       <c r="G63" t="n">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="H63" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>제련</t>
+          <t>요리</t>
         </is>
       </c>
       <c r="J63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K63" t="n">
         <v>18</v>
-      </c>
-      <c r="K63" t="n">
-        <v>40</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
@@ -8977,17 +9213,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rec_GoldIngot</t>
+          <t>Rec_CookedMeat</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>금 주괴</t>
+          <t>구운 고기</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Res_GoldIngot</t>
+          <t>Food_CookedMeat</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -8995,28 +9231,28 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Res_GoldOre x3 + Res_Coal x2</t>
+          <t>Food_RawMeat x1</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>185</v>
+        <v>8</v>
       </c>
       <c r="G64" t="n">
-        <v>326</v>
+        <v>12</v>
       </c>
       <c r="H64" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>제련</t>
+          <t>요리</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
@@ -9025,9 +9261,213 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Rec_Bronze</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>청동 주괴</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Res_Bronze</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Res_CopperOre x3 + Res_TinOre x1 + Res_Coal x1</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>60</v>
+      </c>
+      <c r="G65" t="n">
+        <v>91</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>제련</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>2</v>
+      </c>
+      <c r="K65" t="n">
+        <v>25</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Rec_Steel</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>강철 주괴</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Res_Steel</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Res_IronOre x3 + Res_Coal x2</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>80</v>
+      </c>
+      <c r="G66" t="n">
+        <v>130</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>제련</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>12</v>
+      </c>
+      <c r="K66" t="n">
+        <v>35</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Rec_SilverIngot</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>은 주괴</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Res_SilverIngot</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Res_SilverOre x3 + Res_Coal x1</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>115</v>
+      </c>
+      <c r="G67" t="n">
+        <v>193</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>제련</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>18</v>
+      </c>
+      <c r="K67" t="n">
+        <v>40</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Rec_GoldIngot</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>금 주괴</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Res_GoldIngot</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Res_GoldOre x3 + Res_Coal x2</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>185</v>
+      </c>
+      <c r="G68" t="n">
+        <v>326</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>제련</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>26</v>
+      </c>
+      <c r="K68" t="n">
+        <v>55</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M64"/>
-  <conditionalFormatting sqref="H2:H64">
+  <autoFilter ref="A1:M68"/>
+  <conditionalFormatting sqref="H2:H68">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>1</formula>
     </cfRule>
@@ -9227,7 +9667,11 @@
         <v>5</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
@@ -9867,7 +10311,11 @@
         <v>5</v>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
@@ -9949,7 +10397,11 @@
         <v>40</v>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
@@ -9979,14 +10431,18 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Res_Lumber</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
@@ -10072,7 +10528,11 @@
           <t>Res_Stonecutting</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
@@ -10117,7 +10577,11 @@
           <t>Res_Woodworking</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
@@ -10162,7 +10626,11 @@
           <t>Res_Smelting</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
@@ -10207,7 +10675,11 @@
           <t>Res_Cooking</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
@@ -10252,7 +10724,11 @@
           <t>Res_WeaponSmithing</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
@@ -10293,7 +10769,11 @@
         <v>25</v>
       </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
@@ -10338,7 +10818,11 @@
           <t>Res_Alchemy</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
@@ -10379,7 +10863,11 @@
         <v>25</v>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
@@ -10420,7 +10908,11 @@
         <v>30</v>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
@@ -10484,7 +10976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10578,187 +11070,187 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Biome</t>
+          <t>BandIntent</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Unknown, Plains, Forest, Desert, Tundra, Lava, Cavern, Swamp</t>
+          <t>None, Talk, Attack, Trade, Follow</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Assets/1_Script/World/Biome.cs</t>
+          <t>Assets/1_Script/World/WorldMapView.cs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BodyPartType</t>
+          <t>Biome</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Head, Chest, Abdomen, LeftArm, RightArm, LeftLeg, RightLeg</t>
+          <t>Unknown, Plains, Forest, Desert, Tundra, Lava, Cavern, Swamp</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/BodyPart.cs</t>
+          <t>Assets/1_Script/World/Biome.cs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BuildCategory</t>
+          <t>BodyPartType</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Resource, Defense, Building, Misc</t>
+          <t>Head, Chest, Abdomen, LeftArm, RightArm, LeftLeg, RightLeg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Assets/1_Script/core/BuildCategory.cs</t>
+          <t>Assets/1_Script/unit/BodyPart.cs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CombatStance</t>
+          <t>BuildCategory</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fight, Flee, FightWhileHealthy</t>
+          <t>Resource, Defense, Building, Misc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/AiProfileData.cs</t>
+          <t>Assets/1_Script/core/BuildCategory.cs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CoreType</t>
+          <t>CombatStance</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cave, Meadow, Desert, Swamp, Ice, Lava, Jungle, Cursed</t>
+          <t>Fight, Flee, FightWhileHealthy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Assets/1_Script/core/DungeonCoreData.cs</t>
+          <t>Assets/1_Script/unit/AiProfileData.cs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CraftSkill</t>
+          <t>CoreType</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Labor, WeaponCrafting, ArmorCrafting, Cooking, Alchemy, Research, Smelting, Stonecutting, Woodworking, Gemcutting</t>
+          <t>Cave, Meadow, Desert, Swamp, Ice, Lava, Jungle, Cursed</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/CraftSkill.cs</t>
+          <t>Assets/1_Script/core/DungeonCoreData.cs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DamageCategory</t>
+          <t>CraftSkill</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Physical, Elemental, Dark, Holy</t>
+          <t>Labor, WeaponCrafting, ArmorCrafting, Cooking, Alchemy, Research, Smelting, Stonecutting, Woodworking, Gemcutting</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Combat/DamageCategory.cs</t>
+          <t>Assets/1_Script/Job/CraftSkill.cs</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DamageElement</t>
+          <t>DamageCategory</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None, Fire, Ice, Lightning, Poison</t>
+          <t>Physical, Elemental, Dark, Holy</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Combat/DamageElement.cs</t>
+          <t>Assets/1_Script/Combat/DamageCategory.cs</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FactionStance</t>
+          <t>DamageElement</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ally, Neutral, Hostile</t>
+          <t>None, Fire, Ice, Lightning, Poison</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/FactionData.cs</t>
+          <t>Assets/1_Script/Combat/DamageElement.cs</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FarmState</t>
+          <t>FactionStance</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -10766,119 +11258,119 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Empty, Planted, ReadyToHarvest</t>
+          <t>Ally, Neutral, Hostile</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/FarmPlot.cs</t>
+          <t>Assets/1_Script/unit/FactionData.cs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GameEventType</t>
+          <t>FarmState</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raid, Merchant, Reinforcement, Discovery</t>
+          <t>Empty, Planted, ReadyToHarvest</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Event/GameEventType.cs</t>
+          <t>Assets/1_Script/Job/FarmPlot.cs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GameMode</t>
+          <t>GameEventType</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Field, World</t>
+          <t>Raid, Merchant, Reinforcement, Discovery</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Assets/1_Script/World/GameMode.cs</t>
+          <t>Assets/1_Script/Event/GameEventType.cs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ItemQuality</t>
+          <t>GameMode</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Common, Uncommon, Rare, Unique, Epic, Legendary</t>
+          <t>Field, World</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/ItemQuality.cs</t>
+          <t>Assets/1_Script/World/GameMode.cs</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JobCategory</t>
+          <t>ItemQuality</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None, Mining, Hauling, Farming, Logging, Construction, Guard, Crafting, Research, Unload</t>
+          <t>Common, Uncommon, Rare, Unique, Epic, Legendary</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/JobCategory.cs</t>
+          <t>Assets/1_Script/Item/ItemQuality.cs</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JobStatus</t>
+          <t>JobCategory</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Available, Reserved, InProgress, Done, Cancelled</t>
+          <t>None, Mining, Hauling, Farming, Logging, Construction, Guard, Crafting, Research, Unload, Medical</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/JobBase.cs</t>
+          <t>Assets/1_Script/Job/JobCategory.cs</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MerchantType</t>
+          <t>JobStatus</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -10886,59 +11378,59 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>General, Weapon, Armor, Material, Food</t>
+          <t>Available, Reserved, InProgress, Done, Cancelled</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Event/MerchantData.cs</t>
+          <t>Assets/1_Script/Job/JobBase.cs</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NpcType</t>
+          <t>MerchantType</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Villager, Guard, ShopMerchant, EventMerchant</t>
+          <t>General, Weapon, Armor, Material, Food</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/NpcType.cs</t>
+          <t>Assets/1_Script/Event/MerchantData.cs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PatrolMode</t>
+          <t>NpcType</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Waypoint, Area, Idle</t>
+          <t>Villager, Guard, ShopMerchant, EventMerchant</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/PatrolZone.cs</t>
+          <t>Assets/1_Script/unit/NpcType.cs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PhysicalType</t>
+          <t>PatrolMode</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -10946,59 +11438,59 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Slash, Pierce, Blunt</t>
+          <t>Waypoint, Area, Idle</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Combat/PhysicalType.cs</t>
+          <t>Assets/1_Script/unit/PatrolZone.cs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PlacementMode</t>
+          <t>PhysicalType</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Grid, Free</t>
+          <t>Slash, Pierce, Blunt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Assets/1_Script/BuildModeManager.cs</t>
+          <t>Assets/1_Script/Combat/PhysicalType.cs</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ResourceGroup</t>
+          <t>PlacementMode</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stone, Ore, Gem, Ingot, Wood, Currency</t>
+          <t>Grid, Free</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/ResourceGroup.cs</t>
+          <t>Assets/1_Script/BuildModeManager.cs</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SlotKind</t>
+          <t>ResourceGroup</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -11006,47 +11498,47 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MainHand, OffHand, Head, Chest, Hands, Legs</t>
+          <t>Stone, Ore, Gem, Ingot, Wood, Currency</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Assets/1_Script/UI/EquipSlotUI.cs</t>
+          <t>Assets/1_Script/Item/ResourceGroup.cs</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>StatGrade</t>
+          <t>SlotKind</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FMinus, F, FPlus, EMinus, E, EPlus, DMinus, D, DPlus, CMinus, C, CPlus, BMinus, B, BPlus, AMinus, A, APlus, SMinus, S, SPlus, SSMinus, SS, SSPlus, SSSMinus, SSS, SSSPlus</t>
+          <t>MainHand, OffHand, Head, Chest, Hands, Legs</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/StatGrade.cs</t>
+          <t>Assets/1_Script/UI/EquipSlotUI.cs</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>StatName</t>
+          <t>StatGrade</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Strength, Toughness, Dexterity, Cognition, MeleeAttack, MeleeDefense, RangedDefense, PrecisionShooting, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalMagic, DarkMagic, HolyMagic, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison, MartialArts, Evasion, Athletics, Swimming, Labor, Mining, Growing, Cutting, Taming, Cooking, Medicine, Research, WeaponCrafting, ArmorCrafting, Alchemy, Smelting, Stonecutting, Woodworking, Gemcutting</t>
+          <t>FMinus, F, FPlus, EMinus, E, EPlus, DMinus, D, DPlus, CMinus, C, CPlus, BMinus, B, BPlus, AMinus, A, APlus, SMinus, S, SPlus, SSMinus, SS, SSPlus, SSSMinus, SSS, SSSPlus</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -11058,85 +11550,125 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>StatusEffectType</t>
+          <t>StatName</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Burning, HealReduction, Slowed, Weakened, Shielded, Hasted</t>
+          <t>Strength, Toughness, Dexterity, Cognition, MeleeAttack, MeleeDefense, RangedDefense, PrecisionShooting, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalMagic, DarkMagic, HolyMagic, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison, MartialArts, Evasion, Athletics, Swimming, Labor, Mining, Growing, Cutting, Taming, Cooking, Medicine, Research, WeaponCrafting, ArmorCrafting, Alchemy, Smelting, Stonecutting, Woodworking, Gemcutting</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/StatusEffectType.cs</t>
+          <t>Assets/1_Script/unit/StatGrade.cs</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TileType</t>
+          <t>StatusEffectType</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Impassable, Passable</t>
+          <t>Burning, HealReduction, Slowed, Weakened, Shielded, Hasted</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Map/TileData.cs</t>
+          <t>Assets/1_Script/unit/StatusEffectType.cs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WeaponType</t>
+          <t>TileType</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Unarmed, Shield, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison</t>
+          <t>Impassable, Passable</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/WeaponType.cs</t>
+          <t>Assets/1_Script/Map/TileData.cs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>WeaponType</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>24</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Unarmed, Shield, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Assets/1_Script/Item/WeaponType.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WorldBandBehavior</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Roam, Caravan, Patrol</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Assets/1_Script/World/WorldBandData.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>WorldNodeContent</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B34" t="n">
         <v>6</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Empty, MySettlement, Town, EnemyLair, ResourceSite, Outpost</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Assets/1_Script/World/WorldMap.cs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D32"/>
+  <autoFilter ref="A1:D34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Tools/GameData.xlsx
+++ b/Tools/GameData.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Items'!$A$1:$O$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Recipes'!$A$1:$M$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Buildings'!$A$1:$K$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Enums'!$A$1:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Buildings'!$A$1:$K$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Enums'!$A$1:$D$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9482,7 +9482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9558,17 +9558,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FarmPlot</t>
+          <t>PrisonCage</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>밭</t>
+          <t>우리</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>가구</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -9593,18 +9593,18 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>FarmPlot</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>물</t>
+          <t>밭</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9619,11 +9619,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -9634,18 +9634,18 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TreeBuilding</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>나무 심기</t>
+          <t>물</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9660,11 +9660,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -9679,18 +9679,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>StoneBuilding</t>
+          <t>TreeBuilding</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>돌</t>
+          <t>나무 심기</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9705,29 +9705,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Node_CoalSeam</t>
+          <t>StoneBuilding</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>석탄층</t>
+          <t>돌</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9737,7 +9745,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -9757,18 +9765,18 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Node_CopperVein</t>
+          <t>Node_CoalSeam</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>구리 광맥</t>
+          <t>석탄층</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9798,18 +9806,18 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Node_TinVein</t>
+          <t>Node_CopperVein</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>주석 광맥</t>
+          <t>구리 광맥</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9839,18 +9847,18 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Node_IronVein</t>
+          <t>Node_TinVein</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>철 광맥</t>
+          <t>주석 광맥</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9880,18 +9888,18 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Node_SilverVein</t>
+          <t>Node_IronVein</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>은 광맥</t>
+          <t>철 광맥</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9921,18 +9929,18 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Node_GoldVein</t>
+          <t>Node_SilverVein</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>금 광맥</t>
+          <t>은 광맥</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9962,18 +9970,18 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Node_MagicCrystal</t>
+          <t>Node_GoldVein</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>마력석 결정</t>
+          <t>금 광맥</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9983,7 +9991,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -10003,18 +10011,18 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Node_EtherCrystal</t>
+          <t>Node_MagicCrystal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>에테르석 결정</t>
+          <t>마력석 결정</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10044,18 +10052,18 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Node_VoidCrystal</t>
+          <t>Node_EtherCrystal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공허석 결정</t>
+          <t>에테르석 결정</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10085,18 +10093,18 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Node_RubyVein</t>
+          <t>Node_VoidCrystal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>루비 광맥</t>
+          <t>공허석 결정</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10126,18 +10134,18 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Node_SapphireVein</t>
+          <t>Node_RubyVein</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>사파이어 광맥</t>
+          <t>루비 광맥</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10150,7 +10158,11 @@
           <t>2x1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Res_Stone</t>
+        </is>
+      </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
@@ -10163,18 +10175,18 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Node_TopazVein</t>
+          <t>Node_SapphireVein</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>토파즈 광맥</t>
+          <t>사파이어 광맥</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10200,18 +10212,18 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Node_EmeraldVein</t>
+          <t>Node_TopazVein</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에메랄드 광맥</t>
+          <t>토파즈 광맥</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10237,59 +10249,55 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Node_EmeraldVein</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>바닥</t>
+          <t>에메랄드 광맥</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1x1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Res_Stone</t>
-        </is>
-      </c>
+          <t>2x1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>벽</t>
+          <t>바닥</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -10308,22 +10316,18 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -10362,7 +10366,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="K21" t="n">
         <v>20</v>
       </c>
@@ -10403,7 +10411,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="K22" t="n">
         <v>25</v>
       </c>
@@ -10497,12 +10509,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CraftingTable_Stonecut</t>
+          <t>PrisonBed</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>석재 가공대</t>
+          <t>죄수 침대</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -10512,46 +10524,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>35</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Res_Stonecutting</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CraftingTable_Woodwork</t>
+          <t>CraftingTable_Stonecut</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>제재소</t>
+          <t>석재 가공대</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -10566,15 +10570,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Res_Woodworking</t>
+          <t>Res_Stonecutting</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -10589,18 +10593,18 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CraftingTable_Smelt</t>
+          <t>CraftingTable_Woodwork</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>용광로</t>
+          <t>제재소</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -10610,20 +10614,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Res_Smelting</t>
+          <t>Res_Woodworking</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -10638,18 +10642,18 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CraftingTable_Cook</t>
+          <t>CraftingTable_Smelt</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>조리대</t>
+          <t>용광로</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -10659,20 +10663,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Res_Cooking</t>
+          <t>Res_Smelting</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -10687,18 +10691,18 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CraftingTable_Weapon</t>
+          <t>CraftingTable_Cook</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>무기 제작대</t>
+          <t>조리대</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -10717,11 +10721,11 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Res_WeaponSmithing</t>
+          <t>Res_Cooking</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -10736,18 +10740,18 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CraftingTable_Armor</t>
+          <t>CraftingTable_Weapon</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>방어구 제작대</t>
+          <t>무기 제작대</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -10768,7 +10772,11 @@
       <c r="F30" t="n">
         <v>25</v>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Res_WeaponSmithing</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>O</t>
@@ -10781,18 +10789,18 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CraftingTable_Alchemy</t>
+          <t>CraftingTable_Armor</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>연금술대</t>
+          <t>방어구 제작대</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -10807,17 +10815,13 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Res_CutStone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Res_Alchemy</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>O</t>
@@ -10830,18 +10834,18 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CraftingTable_Gemcut</t>
+          <t>CraftingTable_Alchemy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>보석 연마대</t>
+          <t>연금술대</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -10860,9 +10864,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>25</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Res_Alchemy</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>O</t>
@@ -10875,18 +10883,18 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ResearchTable</t>
+          <t>CraftingTable_Gemcut</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>연구대</t>
+          <t>보석 연마대</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10896,16 +10904,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_CutStone</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
@@ -10920,18 +10928,18 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SubCore</t>
+          <t>ResearchTable</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>서브코어</t>
+          <t>연구대</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10941,16 +10949,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Res_CutStone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
@@ -10959,13 +10967,193 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="K34" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SubCore</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>서브코어</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>보관</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Res_CutStone</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>40</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
         <v>130</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Barricade</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>나무 바리케이드</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Res_Wood</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Palisade</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>목책</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Res_Wood</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>벽</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Res_Stone</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10976,7 +11164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11250,7 +11438,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FactionStance</t>
+          <t>EscortDest</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -11258,19 +11446,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ally, Neutral, Hostile</t>
+          <t>None, Cage, Bed</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/FactionData.cs</t>
+          <t>Assets/1_Script/unit/PrisonEscort.cs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FarmState</t>
+          <t>FactionStance</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -11278,119 +11466,119 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Empty, Planted, ReadyToHarvest</t>
+          <t>Ally, Neutral, Hostile</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/FarmPlot.cs</t>
+          <t>Assets/1_Script/unit/FactionData.cs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GameEventType</t>
+          <t>FarmState</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raid, Merchant, Reinforcement, Discovery</t>
+          <t>Empty, Planted, ReadyToHarvest</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Event/GameEventType.cs</t>
+          <t>Assets/1_Script/Job/FarmPlot.cs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GameMode</t>
+          <t>GameEventType</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Field, World</t>
+          <t>Raid, Merchant, Reinforcement, Discovery</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Assets/1_Script/World/GameMode.cs</t>
+          <t>Assets/1_Script/Event/GameEventType.cs</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ItemQuality</t>
+          <t>GameMode</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Common, Uncommon, Rare, Unique, Epic, Legendary</t>
+          <t>Field, World</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/ItemQuality.cs</t>
+          <t>Assets/1_Script/World/GameMode.cs</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JobCategory</t>
+          <t>ItemQuality</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None, Mining, Hauling, Farming, Logging, Construction, Guard, Crafting, Research, Unload, Medical</t>
+          <t>Common, Uncommon, Rare, Unique, Epic, Legendary</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/JobCategory.cs</t>
+          <t>Assets/1_Script/Item/ItemQuality.cs</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JobStatus</t>
+          <t>JobCategory</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Available, Reserved, InProgress, Done, Cancelled</t>
+          <t>None, Mining, Hauling, Farming, Logging, Construction, Guard, Crafting, Research, Unload, Medical, Warden</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/JobBase.cs</t>
+          <t>Assets/1_Script/Job/JobCategory.cs</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MerchantType</t>
+          <t>JobStatus</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -11398,59 +11586,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>General, Weapon, Armor, Material, Food</t>
+          <t>Available, Reserved, InProgress, Done, Cancelled</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Event/MerchantData.cs</t>
+          <t>Assets/1_Script/Job/JobBase.cs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NpcType</t>
+          <t>MerchantType</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Villager, Guard, ShopMerchant, EventMerchant</t>
+          <t>General, Weapon, Armor, Material, Food</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/NpcType.cs</t>
+          <t>Assets/1_Script/Event/MerchantData.cs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PatrolMode</t>
+          <t>NpcType</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Waypoint, Area, Idle</t>
+          <t>Villager, Guard, ShopMerchant, EventMerchant</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/PatrolZone.cs</t>
+          <t>Assets/1_Script/unit/NpcType.cs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PhysicalType</t>
+          <t>PatrolMode</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -11458,59 +11646,59 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Slash, Pierce, Blunt</t>
+          <t>Waypoint, Area, Idle</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Combat/PhysicalType.cs</t>
+          <t>Assets/1_Script/unit/PatrolZone.cs</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PlacementMode</t>
+          <t>PhysicalType</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Grid, Free</t>
+          <t>Slash, Pierce, Blunt</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Assets/1_Script/BuildModeManager.cs</t>
+          <t>Assets/1_Script/Combat/PhysicalType.cs</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ResourceGroup</t>
+          <t>PlacementMode</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stone, Ore, Gem, Ingot, Wood, Currency</t>
+          <t>Grid, Free</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/ResourceGroup.cs</t>
+          <t>Assets/1_Script/BuildModeManager.cs</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SlotKind</t>
+          <t>ResourceGroup</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -11518,47 +11706,47 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MainHand, OffHand, Head, Chest, Hands, Legs</t>
+          <t>Stone, Ore, Gem, Ingot, Wood, Currency</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Assets/1_Script/UI/EquipSlotUI.cs</t>
+          <t>Assets/1_Script/Item/ResourceGroup.cs</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>StatGrade</t>
+          <t>SlotKind</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FMinus, F, FPlus, EMinus, E, EPlus, DMinus, D, DPlus, CMinus, C, CPlus, BMinus, B, BPlus, AMinus, A, APlus, SMinus, S, SPlus, SSMinus, SS, SSPlus, SSSMinus, SSS, SSSPlus</t>
+          <t>MainHand, OffHand, Head, Chest, Hands, Legs</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/StatGrade.cs</t>
+          <t>Assets/1_Script/UI/EquipSlotUI.cs</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>StatName</t>
+          <t>StatGrade</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Strength, Toughness, Dexterity, Cognition, MeleeAttack, MeleeDefense, RangedDefense, PrecisionShooting, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalMagic, DarkMagic, HolyMagic, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison, MartialArts, Evasion, Athletics, Swimming, Labor, Mining, Growing, Cutting, Taming, Cooking, Medicine, Research, WeaponCrafting, ArmorCrafting, Alchemy, Smelting, Stonecutting, Woodworking, Gemcutting</t>
+          <t>FMinus, F, FPlus, EMinus, E, EPlus, DMinus, D, DPlus, CMinus, C, CPlus, BMinus, B, BPlus, AMinus, A, APlus, SMinus, S, SPlus, SSMinus, SS, SSPlus, SSSMinus, SSS, SSSPlus</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -11570,105 +11758,125 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>StatusEffectType</t>
+          <t>StatName</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Burning, HealReduction, Slowed, Weakened, Shielded, Hasted</t>
+          <t>Strength, Toughness, Dexterity, Cognition, MeleeAttack, MeleeDefense, RangedDefense, PrecisionShooting, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalMagic, DarkMagic, HolyMagic, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison, MartialArts, Evasion, Athletics, Swimming, Labor, Mining, Growing, Cutting, Taming, Cooking, Medicine, Research, WeaponCrafting, ArmorCrafting, Alchemy, Smelting, Stonecutting, Woodworking, Gemcutting, Warden</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/StatusEffectType.cs</t>
+          <t>Assets/1_Script/unit/StatGrade.cs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TileType</t>
+          <t>StatusEffectType</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Impassable, Passable</t>
+          <t>Burning, HealReduction, Slowed, Weakened, Shielded, Hasted</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Map/TileData.cs</t>
+          <t>Assets/1_Script/unit/StatusEffectType.cs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WeaponType</t>
+          <t>TileType</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Unarmed, Shield, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison</t>
+          <t>Impassable, Passable</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/WeaponType.cs</t>
+          <t>Assets/1_Script/Map/TileData.cs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WorldBandBehavior</t>
+          <t>WeaponType</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Roam, Caravan, Patrol</t>
+          <t>Unarmed, Shield, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Assets/1_Script/World/WorldBandData.cs</t>
+          <t>Assets/1_Script/Item/WeaponType.cs</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>WorldBandBehavior</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Roam, Caravan, Patrol</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Assets/1_Script/World/WorldBandData.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>WorldNodeContent</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B35" t="n">
         <v>6</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Empty, MySettlement, Town, EnemyLair, ResourceSite, Outpost</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Assets/1_Script/World/WorldMap.cs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D34"/>
+  <autoFilter ref="A1:D35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Tools/GameData.xlsx
+++ b/Tools/GameData.xlsx
@@ -10,13 +10,17 @@
     <sheet name="Items" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Recipes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Buildings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Enums" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Traits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Backstories" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Enums" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Items'!$A$1:$O$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Items'!$A$1:$P$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Recipes'!$A$1:$M$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Buildings'!$A$1:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Enums'!$A$1:$D$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Traits'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backstories'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Enums'!$A$1:$D$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -464,6 +468,7 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="64" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,6 +547,11 @@
           <t>출처</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -591,6 +601,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>세상 어디서든 통하는 동전. 더블클릭하면 지갑에 들어간다.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -648,6 +663,11 @@
       <c r="O3" t="inlineStr">
         <is>
           <t>JSON</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>두꺼운 생가죽을 오래 두드려 무두질한 것. 강철만큼 막지는 못해도 그만큼 무겁지 않다.</t>
         </is>
       </c>
     </row>
@@ -701,6 +721,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>곰처럼 큰 짐승의 가죽. 무겁고 뻣뻣하지만, 무두질하면 질긴 가죽이 된다.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -760,6 +785,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>짐승에게서 벗겨 무두질한 가죽. 가벼운 방어구의 바탕이 된다.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -817,6 +847,11 @@
       <c r="O6" t="inlineStr">
         <is>
           <t>JSON</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>거칠게 짠 천. 옷과 붕대에 쓴다.</t>
         </is>
       </c>
     </row>
@@ -870,6 +905,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>짐승에게서 막 벗긴 가죽. 이대로는 못 쓴다 — 무두질을 거쳐야 가죽이 된다.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -921,6 +961,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>짐승에게서 발라낸 뼈. 삭아도 남는 것이라 오래된 시체에서도 이것만은 나온다. 단단하고 흔해서 던전 핵이 하수인을 빚는 바탕이 된다.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -980,6 +1025,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>목재 판자. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1037,6 +1087,11 @@
       <c r="O10" t="inlineStr">
         <is>
           <t>SO</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>돌을 다듬어 만든 건축재.</t>
         </is>
       </c>
     </row>
@@ -1090,6 +1145,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>통나무. 켜서 판자로 쓴다.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1141,6 +1201,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>가장 흔한 건축 자재.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1192,6 +1257,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>에테르석. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1243,6 +1313,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>공허석. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1294,6 +1369,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>마력석. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1345,6 +1425,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>금 광석. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1396,6 +1481,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>은 광석. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1447,6 +1537,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>철 광석. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1498,6 +1593,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>주석 광석. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1549,6 +1649,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>구리 광석. 제련하면 청동이 된다.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1600,6 +1705,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>석탄. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1659,6 +1769,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>금 주괴. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1718,6 +1833,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>은 주괴. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1777,6 +1897,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>강철 주괴. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1834,6 +1959,11 @@
       <c r="O25" t="inlineStr">
         <is>
           <t>SO</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>청동 주괴. 채집xB7제련으로 얻는다.</t>
         </is>
       </c>
     </row>
@@ -1887,6 +2017,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>에메랄드. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1938,6 +2073,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>루비. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1989,6 +2129,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>사파이어. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2040,6 +2185,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>토파즈. 채집xB7제련으로 얻는다.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2091,6 +2241,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>물이 덜 마른다 — 어두운 지하 농사에 맞는다.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2142,6 +2297,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>손이 덜 가고 자주 열린다.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2193,6 +2353,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>물을 자주 줘야 한다. 자라면 밀을 거둔다.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2252,6 +2417,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>고기, 채소, 빵이 모두 담긴 성찬. 허기를 완전히 채운다.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2311,6 +2481,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>독을 중화한다. 늪을 지날 땐 반드시 챙긴다.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2370,6 +2545,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>상처가 아무는 속도를 끌어올린다. 마시면 즉시 듣는다.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2429,6 +2609,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>지친 몸을 억지로 깨운다. 오래 걷는 날에.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2488,6 +2673,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>고기와 채소를 넣고 끓인 든든한 한 그릇.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2547,6 +2737,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>숙성시켜 굳힌 것. 진하고 잘 상하지 않는다.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2606,6 +2801,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>신선한 채소로 끓인 수프. 가볍고 부담 없이 허기를 채운다.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2665,6 +2865,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>잘 구운 고기. 허기를 크게 채운다.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2722,6 +2927,11 @@
       <c r="O41" t="inlineStr">
         <is>
           <t>JSON</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>오래 간다. 원정에 들려 보내는 것.</t>
         </is>
       </c>
     </row>
@@ -2775,6 +2985,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>물가에서 얻는다. 구우면 더 낫다.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2832,6 +3047,11 @@
       <c r="O43" t="inlineStr">
         <is>
           <t>SO</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>밀로 구운 주식. 오래 간다.</t>
         </is>
       </c>
     </row>
@@ -2885,6 +3105,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>어두운 곳에서 자란다. 날로도 먹는다.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2942,6 +3167,11 @@
       <c r="O45" t="inlineStr">
         <is>
           <t>JSON</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>허브를 우린 차. 소량의 허기를 채우며 기분을 안정시킨다.</t>
         </is>
       </c>
     </row>
@@ -2995,6 +3225,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>익히지 않은 고기. 구워야 한다.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3046,6 +3281,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>숲에서 바로 따 먹을 수 있다. 조금 찬다.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3097,6 +3337,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>고블린에게서 발라낸 살점. 질기고 냄새가 나 배는 잘 안 찬다 — 푹 끓이면 그나마 먹을 만해진다.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3156,6 +3401,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>루비와 공허석을 융합한 결정. 암흑 화염 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3215,6 +3465,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>사파이어와 공허석을 융합한 결정. 암흑 냉기 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3274,6 +3529,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>토파즈와 공허석을 융합한 결정. 암흑 번개 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3333,6 +3593,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>에메랄드와 공허석을 융합한 결정. 암흑 독 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3392,6 +3657,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>루비와 에테르석을 융합한 결정. 신성 화염 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3451,6 +3721,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>사파이어와 에테르석을 융합한 결정. 신성 냉기 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3510,6 +3785,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>토파즈와 에테르석을 융합한 결정. 신성 번개 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3569,6 +3849,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>에메랄드와 에테르석을 융합한 결정. 신성 독 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3628,6 +3913,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>루비와 마력석을 융합한 결정. 원소 화염 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3687,6 +3977,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>사파이어와 마력석을 융합한 결정. 원소 냉기 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3746,6 +4041,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>토파즈와 마력석을 융합한 결정. 원소 번개 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3805,6 +4105,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>에메랄드와 마력석을 융합한 결정. 원소 독 무기 제작에 사용된다.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3864,6 +4169,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>바늘·실·소독액이 한 벌로 들었다. 빠르고 확실하다.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3923,6 +4233,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>약초를 짓이겨 붙인다. 잘 듣지만 손이 많이 간다.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3982,6 +4297,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>질기게 꼰 줄. 짐을 묶고 발판을 엮는다.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4041,6 +4361,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>삶아 말린 천을 감는다. 제대로 된 치료의 시작.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4100,6 +4425,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>약초에서 뽑아낸 맑은 액체. 모든 조제의 바탕이 된다.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4157,6 +4487,11 @@
       <c r="O66" t="inlineStr">
         <is>
           <t>JSON</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>밀을 빻아 만든 가루. 빵과 요리의 기본 재료.</t>
         </is>
       </c>
     </row>
@@ -4210,6 +4545,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>농사로 수확한 채소류.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4261,6 +4601,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>야생에서 채집한 약초. 차나 포션 재료로 쓴다.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4318,6 +4663,11 @@
       <c r="O69" t="inlineStr">
         <is>
           <t>JSON</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>찢은 천 조각. 급한 대로 상처를 묶는다 — 없는 것보단 낫다.</t>
         </is>
       </c>
     </row>
@@ -4371,6 +4721,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>빻아 빵을 굽는 곡물. 그대로는 먹기 어렵다.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4430,6 +4785,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>무겁지만 확실하다. 급소를 통째로 덮는다.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4489,6 +4849,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>강철 대검.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4548,6 +4913,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>무겁게 내리쳐 갑옷째 부순다. 느리지만 한 방이 크다.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4607,6 +4977,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>짧고 빠르다. 은은 어둠에서 온 것을 태운다.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4666,6 +5041,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>머리를 지킨다. 기절 판정이 잦은 부위라 값어치가 크다.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4725,6 +5105,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>철 갑옷.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4784,6 +5169,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>겹쳐 누빈 두꺼운 가죽. 강철 흉갑의 절반 무게로 그 절반보다 조금 더 막는다.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4843,6 +5233,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>번개 결정을 물린 지팡이. 사거리가 가장 길고, 맞은 것을 잠시 굳힌다.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4902,6 +5297,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>원소 화염 결정을 물린 지팡이. 닿은 것을 태운다.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4961,6 +5361,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>얼려 굳힌다. 화염보다 덜 아프지만 더 오래 붙든다.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5020,6 +5425,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>약하게 자주 맞힌다. 한 방보다 시간이 죽인다.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5079,6 +5489,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>먼저 닿는다. 거리를 유지하며 찌른다.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5138,6 +5553,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>청동검.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5197,6 +5617,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>석궁.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5256,6 +5681,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>가죽 갑옷.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5315,6 +5745,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>철 각반.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5374,6 +5809,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>철 방패.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5433,6 +5873,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>철 철퇴.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5492,6 +5937,11 @@
           <t>SO</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>철검.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5551,6 +6001,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>철 건틀릿.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5610,6 +6065,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>철도끼.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5669,6 +6129,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>당기는 힘이 곧 사거리다. 숙련자만 제 성능을 낸다.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5728,6 +6193,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>장창.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5787,6 +6257,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>가죽 각반.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5846,6 +6321,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>단궁.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5905,6 +6385,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>철 투구.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5964,6 +6449,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>거의 막지 못하지만 아무것도 안 입는 것보단 낫다. 가볍다.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6023,6 +6513,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>가죽 장갑.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6082,6 +6577,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>가죽 모자.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6141,6 +6641,11 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>나무 방패.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6200,9 +6705,14 @@
           <t>JSON</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>굵은 다리뼈를 가죽으로 감아 쥔 것. 잘 들지는 않아도 잘 부러뜨린다 — 죽이기보다 눕히기에 낫다.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O101"/>
+  <autoFilter ref="A1:P101"/>
   <conditionalFormatting sqref="N2:N101">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>1</formula>
@@ -11884,7 +12394,1729 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>배타 묶음</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>스탯 보정</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>파일</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>광부 기질</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>채굴 +15 · 노동 +8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>바위 앞에서 지치지 않는다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Trait_BornMiner</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>용감</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>기질</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>근접공격 +12 · 회피 +5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>앞에 나선다. 겁을 안 내는 만큼 잘 맞기도 한다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Trait_Brave</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>곰손</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>손</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>손재주 -12 · 근력 +8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>손은 둔한 대신 힘으로 밀어붙인다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trait_Clumsy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>겁쟁이</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>기질</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>근접공격 -10 · 육상 +12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>싸움보다 도망이 빠르다. 도망 하나는 누구보다 잘한다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trait_Coward</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>재주꾼</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>손</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>손재주 +15 · 무기제작 +10 · 갑옷제작 +10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>손이 야무지다. 만드는 것마다 모양이 산다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trait_Deft</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>우둔함</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>머리</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>인지력 -10 · 강인함 +8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>머리는 안 돌아가도 몸은 잘 버틴다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Trait_Dull</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>허약</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>체질</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>강인함 -12 · 근접방어 -5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>맷집이 없다. 한 대만 제대로 맞아도 주저앉는다.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trait_Frail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>튼튼한 다리</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>육상 +15 · 수영 +8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>오래 걷고 잘 헤엄친다. 원정에 데려갈 만하다.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trait_Runner</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>명민함</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>머리</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>인지력 +15 · 연구 +12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>이해가 빠르다. 새로운 것을 알아내는 데 강하다.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Trait_Sharp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>강인함</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>체질</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>강인함 +25</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>웬만해선 쓰러지지 않는다. 얻어맞고도 계속 서 있다.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Trait_Tough</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>칸</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>묶음</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>스탯 보정</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>무능력</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>파일</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>도망친 아이</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>회피 +8 · 육상 +6 · 인지력 -4</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>집을 나온 뒤로 돌아가지 않았다. 어디서 잤는지는 기억나지 않는다.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Back_Child_Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>떠돌이 무리에서 자람</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>육상 +8 · 회피 +5 · 원예 -5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>한곳에 두 달을 머문 적이 없다. 짐을 싸는 법부터 배웠다.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Back_Child_Caravan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>빈민가의 아이</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>손재주 +8 · 강인함 +5 · 사교 -4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>담벼락 아래에서 컸다. 나눠 주는 사람은 없었고 뺏는 사람만 있었다.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Back_Child_Slum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>주정뱅이의 자식</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>강인함 +10 · 사교 -6</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>맞으면서 자랐다. 맞는 데는 이골이 났다.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Back_Child_Drunk</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>거리의 아이</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>회피 +8 · 손재주 +5 · 사교 -4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>골목에서 자랐다. 뺏기지 않으려면 빨라야 했고, 얻으려면 손이 빨라야 했다.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Back_Child_Street</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>광산 마을 출신</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>채굴 +12 · 강인함 +5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>갱도의 공기를 마시며 자랐다. 어두운 곳이 무섭지 않다.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Back_Child_Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>귀족가의 아이</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>사교 +10 · 인지력 +6 · 근력 -8</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>운반</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>글과 예법을 배웠다. 짐을 지어 본 적은 한 번도 없다.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Back_Child_Noble</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>농가의 막내</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>원예 +10 · 근력 +5 · 인지력 -4</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>해 뜨면 밭에 나갔다. 흙이 무엇을 원하는지는 배우기 전에 알았다.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Back_Child_Farm</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>대장간 도제</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>무기제작 +8 · 제련 +6 · 사교 -3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>풀무질부터 배웠다. 쇠가 언제 준비됐는지는 색으로 안다.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Back_Child_Smithy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>사원의 시동</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>연구 +8 · 의료 +5 · 근접공격 -4</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>약초와 필사를 배웠다. 사람을 때리는 법은 배우지 않았다.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Back_Child_Temple</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>숲에서 자람</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>벌목 +8 · 활 +6 · 사교 -5</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>나무와 짐승 사이에서 컸다. 사람 사이가 오히려 어렵다.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Back_Child_Forest</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cult</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>교단 마을에서 자람</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>암흑마법 +7 · 인지력 +5 · 사교 -4</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>마을 사람 모두가 같은 것을 믿었다. 다른 믿음은 본 적이 없다.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Back_Child_CultTown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cult</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>밤에 끌려간 아이</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>강인함 +8 · 암흑마법 +6 · 사교 -8</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>누군가 데려갔고 아무도 찾지 않았다. 그 뒤의 일은 말하지 않는다.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Back_Child_Taken</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cult</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>제단에 놓인 아이</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>암흑마법 +8 · 강인함 +5 · 원예 -5</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>누가 두고 갔는지 아무도 모른다. 교단이 거두어 길렀다.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Back_Child_Foundling</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>mercenary</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>고아원 출신</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>근접방어 +7 · 강인함 +5 · 인지력 -4</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>열여섯이 되자 나가라고 했다. 받아 주는 곳은 용병단뿐이었다.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Back_Child_Orphan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>유년기</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>mercenary</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>병영에서 자람</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>근접공격 +8 · 강인함 +5 · 연구 -5</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>아버지의 부대를 따라다녔다. 검을 장난감으로 알고 컸다.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Back_Child_Barrack</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>노상강도</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>활 +10 · 회피 +5 · 사교 -5</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>숲길 모퉁이에서 기다렸다. 활을 먼저 보이면 대개 짐만 두고 갔다.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Back_Adult_Highway</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>도굴꾼</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>손재주 +10 · 회피 +6 · 사교 -6</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>무덤을 열어 먹고살았다. 그 일로 잃은 것은 손이 아니라 이름이다.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Back_Adult_Robber</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>밀수꾼</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>사교 +8 · 손재주 +6 · 육상 +4</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>검문을 피해 물건을 옮겼다. 값이 되는 것이라면 무엇이든.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Back_Adult_Smuggler</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>산적</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>근접공격 +8 · 회피 +6 · 사교 -6</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>길목에 앉아 지나가는 것을 받아먹었다. 처음엔 굶어서였다.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Back_Adult_Bandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>옥살이</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>강인함 +10 · 회피 +4 · 사교 -8</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>간수</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>몇 해를 갇혀 지냈다. 창살 안쪽이 어떤 곳인지 알아서, 남을 가둬 두지 못한다.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Back_Adult_Convict</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>탈영병</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>장창 +10 · 근접방어 +6 · 사교 -4</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>부대를 버리고 도망쳤다. 다루는 법만은 그대로 남았다.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Back_Adult_Deserter</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>패거리 두목</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>근접공격 +10 · 사교 +8 · 강인함 +6</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>열몇을 먹여 살렸다. 그 방법이 남의 것을 뺏는 것이었을 뿐이다.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Back_Adult_Chief</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>광부</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>채굴 +14 · 근력 +8 · 사교 -4</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>곡괭이만 쥐고 살았다. 어깨가 그만큼 굽었다.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Back_Adult_Miner</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>떠돌이 의원</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>의료 +14 · 연금 +6 · 근력 -4</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>마을을 옮겨 다니며 상처를 꿰맸다. 값은 대개 밥이었다.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Back_Adult_Medic</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>밭갈이꾼</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>원예 +12 · 근력 +6</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>한 뙈기를 평생 갈았다. 그 땅이 남의 것이 되기 전까지는.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Back_Adult_Farmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>상단 호위</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>사교 +8 · 근접방어 +6 · 육상 +4</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>짐과 사람을 함께 지켰다. 길 위에서는 말이 칼보다 자주 쓰인다.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Back_Adult_Guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>요리사</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>요리 +14 · 손재주 +5</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>여관 부엌을 맡았다. 무엇이든 먹을 것으로 만드는 재주가 있다.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Back_Adult_Cook</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>civilian</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>학자</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>연구 +14 · 인지력 +8 · 근력 -6</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>경비</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>책과 도면 사이에서 늙었다. 창을 쥐어 줘도 어디를 봐야 할지 모른다.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Back_Adult_Scholar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>cult</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>교단의 신도</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>암흑마법 +12 · 인지력 +6 · 사교 -8</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>밤마다 무언가를 불렀다. 대답이 있었는지는 말하지 않는다.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Back_Adult_Cultist</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>cult</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>시신을 나르던 자</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>의료 +8 · 근력 +6 · 사교 -6</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>교단이 원하는 것을 구해다 주었다. 무엇에 쓰는지는 묻지 않았다.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Back_Adult_Graverob</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>cult</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>주문 필사자</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>암흑마법 +10 · 연구 +8 · 근력 -5</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>읽어서는 안 되는 것을 베껴 적었다. 손은 아직도 가끔 떨린다.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Back_Adult_Scribe</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>mercenary</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>야영 취사병</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>요리 +12 · 강인함 +5 · 근접공격 -5</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>부대의 배를 채웠다. 싸운 적은 없지만 싸움터에는 늘 있었다.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Back_Adult_Camp</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>mercenary</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>용병</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>근접공격 +10 · 강인함 +6 · 사교 -4</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>값을 받고 싸웠다. 누구 편이었는지는 그때마다 달랐다.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Back_Adult_Merc</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>mercenary</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>용병단 소속</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>근접공격 +9 · 근접방어 +7 · 사교 +4</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>계약서대로 싸웠고 계약서대로 물러났다. 그 이상도 이하도 아니다.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Back_Adult_Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>성년기</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>mercenary</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>창병 대열</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>장창 +12 · 근접방어 +8 · 회피 -4</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>줄을 맞춰 서서 버티는 법을 배웠다. 혼자 싸우는 법은 배우지 않았다.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Back_Adult_Pikeman</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H37"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11978,207 +14210,207 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BandIntent</t>
+          <t>BackstorySlot</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None, Talk, Attack, Trade, Follow</t>
+          <t>Childhood, Adulthood</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Assets/1_Script/World/WorldMapView.cs</t>
+          <t>Assets/1_Script/unit/BackstoryData.cs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biome</t>
+          <t>BandIntent</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Unknown, Plains, Forest, Desert, Tundra, Lava, Cavern, Swamp</t>
+          <t>None, Talk, Attack, Trade, Follow</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Assets/1_Script/World/Biome.cs</t>
+          <t>Assets/1_Script/World/WorldMapView.cs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BodyPartType</t>
+          <t>Biome</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Head, Chest, Abdomen, LeftArm, RightArm, LeftLeg, RightLeg</t>
+          <t>Unknown, Plains, Forest, Desert, Tundra, Lava, Cavern, Swamp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/BodyPart.cs</t>
+          <t>Assets/1_Script/World/Biome.cs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BuildCategory</t>
+          <t>BodyPartType</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Resource, Defense, Building, Misc</t>
+          <t>Head, Chest, Abdomen, LeftArm, RightArm, LeftLeg, RightLeg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Assets/1_Script/core/BuildCategory.cs</t>
+          <t>Assets/1_Script/unit/BodyPart.cs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CombatStance</t>
+          <t>BuildCategory</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fight, Flee, FightWhileHealthy</t>
+          <t>Resource, Defense, Building, Misc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/AiProfileData.cs</t>
+          <t>Assets/1_Script/core/BuildCategory.cs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CoreType</t>
+          <t>CombatStance</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cave, Meadow, Desert, Swamp, Ice, Lava, Jungle, Cursed</t>
+          <t>Fight, Flee, FightWhileHealthy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Assets/1_Script/core/DungeonCoreData.cs</t>
+          <t>Assets/1_Script/unit/AiProfileData.cs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CorpseStage</t>
+          <t>CoreType</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fresh, Rotten, Bones</t>
+          <t>Cave, Meadow, Desert, Swamp, Ice, Lava, Jungle, Cursed</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/Corpse.cs</t>
+          <t>Assets/1_Script/core/DungeonCoreData.cs</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CraftSkill</t>
+          <t>CorpseStage</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Labor, WeaponCrafting, ArmorCrafting, Cooking, Alchemy, Research, Smelting, Stonecutting, Woodworking, Gemcutting</t>
+          <t>Fresh, Rotten, Bones</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/CraftSkill.cs</t>
+          <t>Assets/1_Script/unit/Corpse.cs</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DamageCategory</t>
+          <t>CraftSkill</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Physical, Elemental, Dark, Holy</t>
+          <t>Labor, WeaponCrafting, ArmorCrafting, Cooking, Alchemy, Research, Smelting, Stonecutting, Woodworking, Gemcutting</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Combat/DamageCategory.cs</t>
+          <t>Assets/1_Script/Job/CraftSkill.cs</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DamageElement</t>
+          <t>DamageCategory</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None, Fire, Ice, Lightning, Poison</t>
+          <t>Physical, Elemental, Dark, Holy</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Combat/DamageElement.cs</t>
+          <t>Assets/1_Script/Combat/DamageCategory.cs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EscortDest</t>
+          <t>DamageElement</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -12186,39 +14418,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None, Cage, Bed, Grave, Pyre</t>
+          <t>None, Fire, Ice, Lightning, Poison</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/PrisonEscort.cs</t>
+          <t>Assets/1_Script/Combat/DamageElement.cs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FactionStance</t>
+          <t>EscortDest</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ally, Neutral, Hostile</t>
+          <t>None, Cage, Bed, Grave, Pyre</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/FactionData.cs</t>
+          <t>Assets/1_Script/unit/PrisonEscort.cs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FarmState</t>
+          <t>FactionStance</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -12226,119 +14458,119 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Empty, Planted, ReadyToHarvest</t>
+          <t>Ally, Neutral, Hostile</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/FarmPlot.cs</t>
+          <t>Assets/1_Script/unit/FactionData.cs</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GameEventType</t>
+          <t>FarmState</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raid, Merchant, Reinforcement, Discovery</t>
+          <t>Empty, Planted, ReadyToHarvest</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Event/GameEventType.cs</t>
+          <t>Assets/1_Script/Job/FarmPlot.cs</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GameMode</t>
+          <t>GameEventType</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Field, World</t>
+          <t>Raid, Merchant, Reinforcement, Discovery</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Assets/1_Script/World/GameMode.cs</t>
+          <t>Assets/1_Script/Event/GameEventType.cs</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ItemQuality</t>
+          <t>GameMode</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Common, Uncommon, Rare, Unique, Epic, Legendary</t>
+          <t>Field, World</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/ItemQuality.cs</t>
+          <t>Assets/1_Script/World/GameMode.cs</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JobCategory</t>
+          <t>ItemQuality</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None, Mining, Hauling, Farming, Logging, Construction, Guard, Crafting, Research, Unload, Medical, Warden, Butcher</t>
+          <t>Common, Uncommon, Rare, Unique, Epic, Legendary</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/JobCategory.cs</t>
+          <t>Assets/1_Script/Item/ItemQuality.cs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JobStatus</t>
+          <t>JobCategory</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Available, Reserved, InProgress, Done, Cancelled</t>
+          <t>None, Mining, Hauling, Farming, Logging, Construction, Guard, Crafting, Research, Unload, Medical, Warden, Butcher</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/JobBase.cs</t>
+          <t>Assets/1_Script/Job/JobCategory.cs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MerchantType</t>
+          <t>JobStatus</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -12346,19 +14578,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>General, Weapon, Armor, Material, Food</t>
+          <t>Available, Reserved, InProgress, Done, Cancelled</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Event/MerchantData.cs</t>
+          <t>Assets/1_Script/Job/JobBase.cs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NpcType</t>
+          <t>MerchantType</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -12366,39 +14598,39 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Villager, Guard, ShopMerchant, EventMerchant, Drifter</t>
+          <t>General, Weapon, Armor, Material, Food</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/NpcType.cs</t>
+          <t>Assets/1_Script/Event/MerchantData.cs</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PatrolMode</t>
+          <t>NpcType</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Waypoint, Area, Idle</t>
+          <t>Villager, Guard, ShopMerchant, EventMerchant, Drifter</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/PatrolZone.cs</t>
+          <t>Assets/1_Script/unit/NpcType.cs</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PhysicalType</t>
+          <t>PatrolMode</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -12406,39 +14638,39 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slash, Pierce, Blunt</t>
+          <t>Waypoint, Area, Idle</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Combat/PhysicalType.cs</t>
+          <t>Assets/1_Script/unit/PatrolZone.cs</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PlacementMode</t>
+          <t>PhysicalType</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grid, Free</t>
+          <t>Slash, Pierce, Blunt</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Assets/1_Script/BuildModeManager.cs</t>
+          <t>Assets/1_Script/Combat/PhysicalType.cs</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Repeat</t>
+          <t>PlacementMode</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -12446,107 +14678,107 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Forever, Count</t>
+          <t>Grid, Free</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/ButcherBill.cs</t>
+          <t>Assets/1_Script/BuildModeManager.cs</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ResourceGroup</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stone, Ore, Gem, Ingot, Wood, Currency</t>
+          <t>Forever, Count</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/ResourceGroup.cs</t>
+          <t>Assets/1_Script/Job/ButcherBill.cs</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ripeness</t>
+          <t>ResourceGroup</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FreshOnly, NotBones, Any</t>
+          <t>Stone, Ore, Gem, Ingot, Wood, Currency</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/ButcherBill.cs</t>
+          <t>Assets/1_Script/Item/ResourceGroup.cs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SlotKind</t>
+          <t>Ripeness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MainHand, OffHand, Head, Chest, Hands, Legs</t>
+          <t>FreshOnly, NotBones, Any</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Assets/1_Script/UI/EquipSlotUI.cs</t>
+          <t>Assets/1_Script/Job/ButcherBill.cs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>StatGrade</t>
+          <t>SlotKind</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FMinus, F, FPlus, EMinus, E, EPlus, DMinus, D, DPlus, CMinus, C, CPlus, BMinus, B, BPlus, AMinus, A, APlus, SMinus, S, SPlus, SSMinus, SS, SSPlus, SSSMinus, SSS, SSSPlus</t>
+          <t>MainHand, OffHand, Head, Chest, Hands, Legs</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/StatGrade.cs</t>
+          <t>Assets/1_Script/UI/EquipSlotUI.cs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>StatName</t>
+          <t>StatGrade</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Strength, Toughness, Dexterity, Cognition, MeleeAttack, MeleeDefense, RangedDefense, PrecisionShooting, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalMagic, DarkMagic, HolyMagic, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison, MartialArts, Evasion, Athletics, Swimming, Labor, Mining, Growing, Cutting, Taming, Cooking, Medicine, Research, WeaponCrafting, ArmorCrafting, Alchemy, Smelting, Stonecutting, Woodworking, Gemcutting, Social</t>
+          <t>FMinus, F, FPlus, EMinus, E, EPlus, DMinus, D, DPlus, CMinus, C, CPlus, BMinus, B, BPlus, AMinus, A, APlus, SMinus, S, SPlus, SSMinus, SS, SSPlus, SSSMinus, SSS, SSSPlus</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -12558,47 +14790,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>StatusEffectType</t>
+          <t>StatName</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Burning, HealReduction, Slowed, Weakened, Shielded, Hasted</t>
+          <t>Strength, Toughness, Dexterity, Cognition, MeleeAttack, MeleeDefense, RangedDefense, PrecisionShooting, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalMagic, DarkMagic, HolyMagic, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison, MartialArts, Evasion, Athletics, Swimming, Labor, Mining, Growing, Cutting, Taming, Cooking, Medicine, Research, WeaponCrafting, ArmorCrafting, Alchemy, Smelting, Stonecutting, Woodworking, Gemcutting, Social</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/StatusEffectType.cs</t>
+          <t>Assets/1_Script/unit/StatGrade.cs</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>StockView</t>
+          <t>StatusEffectType</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cells, Cards</t>
+          <t>Burning, HealReduction, Slowed, Weakened, Shielded, Hasted</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Assets/1_Script/UI/MerchantUI.cs</t>
+          <t>Assets/1_Script/unit/StatusEffectType.cs</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TileType</t>
+          <t>StockView</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -12606,79 +14838,79 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Impassable, Passable</t>
+          <t>Cells, Cards</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Map/TileData.cs</t>
+          <t>Assets/1_Script/UI/MerchantUI.cs</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TimePhase</t>
+          <t>TileType</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dawn, Morning, Day, Evening, Night</t>
+          <t>Impassable, Passable</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Assets/1_Script/GameTimeManager.cs</t>
+          <t>Assets/1_Script/Map/TileData.cs</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WeaponType</t>
+          <t>TimePhase</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Unarmed, Shield, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison</t>
+          <t>Dawn, Morning, Day, Evening, Night</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/WeaponType.cs</t>
+          <t>Assets/1_Script/GameTimeManager.cs</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Whom</t>
+          <t>WeaponType</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hostile, NotMine, Everyone</t>
+          <t>Unarmed, Shield, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/ButcherBill.cs</t>
+          <t>Assets/1_Script/Item/WeaponType.cs</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WorldBandBehavior</t>
+          <t>Whom</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -12686,37 +14918,57 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Roam, Caravan, Patrol</t>
+          <t>Hostile, NotAllied, Everyone</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Assets/1_Script/World/WorldBandData.cs</t>
+          <t>Assets/1_Script/Job/ButcherBill.cs</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>WorldBandBehavior</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Roam, Caravan, Patrol</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Assets/1_Script/World/WorldBandData.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>WorldNodeContent</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B42" t="n">
         <v>6</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Empty, MySettlement, Town, EnemyLair, ResourceSite, Outpost</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Assets/1_Script/World/WorldMap.cs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D41"/>
+  <autoFilter ref="A1:D42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Tools/GameData.xlsx
+++ b/Tools/GameData.xlsx
@@ -15,12 +15,12 @@
     <sheet name="Enums" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Items'!$A$1:$P$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Recipes'!$A$1:$M$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Buildings'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Items'!$A$1:$P$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Recipes'!$A$1:$M$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Buildings'!$A$1:$K$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Traits'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backstories'!$A$1:$H$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Enums'!$A$1:$D$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Enums'!$A$1:$D$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3346,12 +3346,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>crystal_dark_fire</t>
+          <t>crystal_arcane</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>암흑 화염 결정</t>
+          <t>비전 결정</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="E49" t="n">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F49" t="n">
         <v>2</v>
@@ -3375,7 +3375,7 @@
         <v>0.2</v>
       </c>
       <c r="I49" t="n">
-        <v>1785</v>
+        <v>1680</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -3387,14 +3387,14 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Res_Ruby x1 + Res_Voidstone x1</t>
+          <t>Res_MagicStone x2</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="N49" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3403,19 +3403,19 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>루비와 공허석을 융합한 결정. 암흑 화염 무기 제작에 사용된다.</t>
+          <t>비전의 힘을 가둔 결정. 같은 속성 지팡이를 만드는 데 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>crystal_dark_ice</t>
+          <t>crystal_dark</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>암흑 냉기 결정</t>
+          <t>공허 결정</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="E50" t="n">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F50" t="n">
         <v>2</v>
@@ -3439,7 +3439,7 @@
         <v>0.2</v>
       </c>
       <c r="I50" t="n">
-        <v>1785</v>
+        <v>1660</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
@@ -3451,14 +3451,14 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Res_Sapphire x1 + Res_Voidstone x1</t>
+          <t>Res_Voidstone x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="N50" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3467,19 +3467,19 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>사파이어와 공허석을 융합한 결정. 암흑 냉기 무기 제작에 사용된다.</t>
+          <t>공허의 힘을 가둔 결정. 같은 속성 지팡이를 만드는 데 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>crystal_dark_lightning</t>
+          <t>crystal_holy</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>암흑 번개 결정</t>
+          <t>성광 결정</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="E51" t="n">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="F51" t="n">
         <v>2</v>
@@ -3503,7 +3503,7 @@
         <v>0.2</v>
       </c>
       <c r="I51" t="n">
-        <v>1785</v>
+        <v>1640</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -3515,14 +3515,14 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Res_Topaz x1 + Res_Voidstone x1</t>
+          <t>Res_Etherstone x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="N51" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3531,19 +3531,19 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>토파즈와 공허석을 융합한 결정. 암흑 번개 무기 제작에 사용된다.</t>
+          <t>성광의 힘을 가둔 결정. 같은 속성 지팡이를 만드는 데 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>crystal_dark_poison</t>
+          <t>crystal_lightning</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>암흑 독 결정</t>
+          <t>뇌전 결정</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="E52" t="n">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="F52" t="n">
         <v>2</v>
@@ -3567,7 +3567,7 @@
         <v>0.2</v>
       </c>
       <c r="I52" t="n">
-        <v>1785</v>
+        <v>1610</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -3579,14 +3579,14 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Res_Emerald x1 + Res_Voidstone x1</t>
+          <t>Res_Topaz x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="N52" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3595,19 +3595,19 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>에메랄드와 공허석을 융합한 결정. 암흑 독 무기 제작에 사용된다.</t>
+          <t>뇌전의 힘을 가둔 결정. 같은 속성 지팡이를 만드는 데 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>crystal_holy_fire</t>
+          <t>crystal_fire</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>신성 화염 결정</t>
+          <t>화염 결정</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>357</v>
+        <v>314</v>
       </c>
       <c r="E53" t="n">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
@@ -3631,7 +3631,7 @@
         <v>0.2</v>
       </c>
       <c r="I53" t="n">
-        <v>1785</v>
+        <v>1570</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -3643,14 +3643,14 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Res_Ruby x1 + Res_Etherstone x1</t>
+          <t>Res_Ruby x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="N53" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3659,19 +3659,19 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>루비와 에테르석을 융합한 결정. 신성 화염 무기 제작에 사용된다.</t>
+          <t>화염의 힘을 가둔 결정. 같은 속성 지팡이를 만드는 데 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>crystal_holy_ice</t>
+          <t>crystal_earth</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>신성 냉기 결정</t>
+          <t>지반 결정</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>357</v>
+        <v>311</v>
       </c>
       <c r="E54" t="n">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="F54" t="n">
         <v>2</v>
@@ -3695,7 +3695,7 @@
         <v>0.2</v>
       </c>
       <c r="I54" t="n">
-        <v>1785</v>
+        <v>1555</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -3707,14 +3707,14 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Res_Sapphire x1 + Res_Etherstone x1</t>
+          <t>Res_Emerald x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="N54" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3723,19 +3723,19 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>사파이어와 에테르석을 융합한 결정. 신성 냉기 무기 제작에 사용된다.</t>
+          <t>지반의 힘을 가둔 결정. 같은 속성 지팡이를 만드는 데 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>crystal_holy_lightning</t>
+          <t>crystal_water</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>신성 번개 결정</t>
+          <t>해류 결정</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>357</v>
+        <v>301</v>
       </c>
       <c r="E55" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="F55" t="n">
         <v>2</v>
@@ -3759,7 +3759,7 @@
         <v>0.2</v>
       </c>
       <c r="I55" t="n">
-        <v>1785</v>
+        <v>1505</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -3771,14 +3771,14 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Res_Topaz x1 + Res_Etherstone x1</t>
+          <t>Res_Sapphire x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="N55" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3787,19 +3787,19 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>토파즈와 에테르석을 융합한 결정. 신성 번개 무기 제작에 사용된다.</t>
+          <t>해류의 힘을 가둔 결정. 같은 속성 지팡이를 만드는 데 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>crystal_holy_poison</t>
+          <t>med_kit</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>신성 독 결정</t>
+          <t>구급낭</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>357</v>
+        <v>165</v>
       </c>
       <c r="E56" t="n">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
@@ -3820,29 +3820,29 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="I56" t="n">
-        <v>1785</v>
+        <v>206.2</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Res_Emerald x1 + Res_Etherstone x1</t>
+          <t>med_bandage x3 + herbs x2 + alch_essence x1</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>210</v>
+        <v>96</v>
       </c>
       <c r="N56" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3851,19 +3851,19 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>에메랄드와 에테르석을 융합한 결정. 신성 독 무기 제작에 사용된다.</t>
+          <t>바늘·실·소독액이 한 벌로 들었다. 빠르고 확실하다.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>crystal_elemental_fire</t>
+          <t>med_poultice</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>원소 화염 결정</t>
+          <t>약초 습포</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>285</v>
+        <v>58</v>
       </c>
       <c r="E57" t="n">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
@@ -3884,29 +3884,29 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I57" t="n">
-        <v>1425</v>
+        <v>193.3</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Res_Ruby x1 + Res_MagicStone x1</t>
+          <t>herbs x3 + med_bandage x1</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="N57" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3915,19 +3915,19 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>루비와 마력석을 융합한 결정. 원소 화염 무기 제작에 사용된다.</t>
+          <t>약초를 짓이겨 붙인다. 잘 듣지만 손이 많이 간다.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>crystal_elemental_ice</t>
+          <t>rope</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>원소 냉기 결정</t>
+          <t>밧줄</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>285</v>
+        <v>42</v>
       </c>
       <c r="E58" t="n">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="F58" t="n">
         <v>2</v>
@@ -3948,26 +3948,26 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>1425</v>
+        <v>84</v>
       </c>
       <c r="J58" t="n">
         <v>1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Res_Sapphire x1 + Res_MagicStone x1</t>
+          <t>cloth x2</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>190</v>
+        <v>28</v>
       </c>
       <c r="N58" t="n">
         <v>1.5</v>
@@ -3979,19 +3979,19 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>사파이어와 마력석을 융합한 결정. 원소 냉기 무기 제작에 사용된다.</t>
+          <t>질기게 꼰 줄. 짐을 묶고 발판을 엮는다.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>crystal_elemental_lightning</t>
+          <t>med_bandage</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>원소 번개 결정</t>
+          <t>붕대</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>285</v>
+        <v>22</v>
       </c>
       <c r="E59" t="n">
-        <v>142</v>
+        <v>11</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -4015,7 +4015,7 @@
         <v>0.2</v>
       </c>
       <c r="I59" t="n">
-        <v>1425</v>
+        <v>110</v>
       </c>
       <c r="J59" t="n">
         <v>1</v>
@@ -4027,14 +4027,14 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Res_Topaz x1 + Res_MagicStone x1</t>
+          <t>cloth x2</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="N59" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4043,19 +4043,19 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>토파즈와 마력석을 융합한 결정. 원소 번개 무기 제작에 사용된다.</t>
+          <t>삶아 말린 천을 감는다. 제대로 된 치료의 시작.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>crystal_elemental_poison</t>
+          <t>alch_essence</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>원소 독 결정</t>
+          <t>정제 정수</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>285</v>
+        <v>18</v>
       </c>
       <c r="E60" t="n">
-        <v>142</v>
+        <v>9</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
@@ -4076,10 +4076,10 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I60" t="n">
-        <v>1425</v>
+        <v>180</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
@@ -4091,11 +4091,11 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Res_Emerald x1 + Res_MagicStone x1</t>
+          <t>herbs x2</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>190</v>
+        <v>12</v>
       </c>
       <c r="N60" t="n">
         <v>1.5</v>
@@ -4107,19 +4107,19 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>에메랄드와 마력석을 융합한 결정. 원소 독 무기 제작에 사용된다.</t>
+          <t>약초에서 뽑아낸 맑은 액체. 모든 조제의 바탕이 된다.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>med_kit</t>
+          <t>flour</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>구급낭</t>
+          <t>밀가루</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4128,41 +4128,41 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>165</v>
+        <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="I61" t="n">
-        <v>206.2</v>
+        <v>45</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>med_bandage x3 + herbs x2 + alch_essence x1</t>
+          <t>Crop_Wheat x3</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="N61" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4171,19 +4171,19 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>바늘·실·소독액이 한 벌로 들었다. 빠르고 확실하다.</t>
+          <t>밀을 빻아 만든 가루. 빵과 요리의 기본 재료.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>med_poultice</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>약초 습포</t>
+          <t>채소</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
         <v>2</v>
@@ -4207,27 +4207,19 @@
         <v>0.3</v>
       </c>
       <c r="I62" t="n">
-        <v>193.3</v>
+        <v>26.7</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1x2</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>herbs x3 + med_bandage x1</t>
-        </is>
-      </c>
-      <c r="M62" t="n">
-        <v>20</v>
-      </c>
-      <c r="N62" t="n">
-        <v>2.9</v>
-      </c>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -4235,19 +4227,19 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>약초를 짓이겨 붙인다. 잘 듣지만 손이 많이 간다.</t>
+          <t>농사로 수확한 채소류.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rope</t>
+          <t>herbs</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>밧줄</t>
+          <t>허브</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4256,10 +4248,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F63" t="n">
         <v>2</v>
@@ -4268,30 +4260,22 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="I63" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1x2</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>cloth x2</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>28</v>
-      </c>
-      <c r="N63" t="n">
-        <v>1.5</v>
-      </c>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -4299,19 +4283,19 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>질기게 꼰 줄. 짐을 묶고 발판을 엮는다.</t>
+          <t>야생에서 채집한 약초. 차나 포션 재료로 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>med_bandage</t>
+          <t>med_rag</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>붕대</t>
+          <t>넝마</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4320,10 +4304,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>2</v>
@@ -4332,10 +4316,10 @@
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I64" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="J64" t="n">
         <v>1</v>
@@ -4347,14 +4331,14 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>cloth x2</t>
+          <t>cloth x1</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N64" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4363,19 +4347,19 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>삶아 말린 천을 감는다. 제대로 된 치료의 시작.</t>
+          <t>찢은 천 조각. 급한 대로 상처를 묶는다 — 없는 것보단 낫다.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>alch_essence</t>
+          <t>Crop_Wheat</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>정제 정수</t>
+          <t>밀</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4384,10 +4368,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>2</v>
@@ -4396,93 +4380,85 @@
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I65" t="n">
-        <v>180</v>
+        <v>13.3</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>1x1</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>herbs x2</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
-        <v>12</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>약초에서 뽑아낸 맑은 액체. 모든 조제의 바탕이 된다.</t>
+          <t>빻아 빵을 굽는 곡물. 그대로는 먹기 어렵다.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>arm_steel_chest</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>밀가루</t>
+          <t>강철 흉갑</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>잡화</t>
+          <t>몸통 방어구</t>
         </is>
       </c>
       <c r="D66" t="n">
+        <v>1256</v>
+      </c>
+      <c r="E66" t="n">
+        <v>314</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H66" t="n">
         <v>9</v>
       </c>
-      <c r="E66" t="n">
-        <v>4</v>
-      </c>
-      <c r="F66" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.2</v>
-      </c>
       <c r="I66" t="n">
-        <v>45</v>
+        <v>139.6</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Crop_Wheat x3</t>
+          <t>Res_Steel x5 + leather x2</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>6</v>
+        <v>698</v>
       </c>
       <c r="N66" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4491,55 +4467,63 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>밀을 빻아 만든 가루. 빵과 요리의 기본 재료.</t>
+          <t>무겁지만 확실하다. 급소를 통째로 덮는다.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>vegetables</t>
+          <t>Wpn_SteelSword</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>채소</t>
+          <t>강철 대검</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>잡화</t>
+          <t>양손 검</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>992</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>273</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="H67" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
-        <v>26.7</v>
+        <v>198.4</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1x1</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>2x4</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Res_Steel x4 + Res_Lumber x2</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>536</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1.85</v>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -4547,55 +4531,63 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>농사로 수확한 채소류.</t>
+          <t>강철 대검.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>herbs</t>
+          <t>wpn_steel_axe</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>허브</t>
+          <t>강철 도끼</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>잡화</t>
+          <t>양손 도끼</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>710</v>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>195</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="I68" t="n">
-        <v>60</v>
+        <v>208.8</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1x1</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>2x4</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Res_Steel x3 + Res_Lumber x2</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>406</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1.75</v>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -4603,62 +4595,62 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>야생에서 채집한 약초. 차나 포션 재료로 쓴다.</t>
+          <t>무겁게 내리쳐 갑옷째 부순다. 느리지만 한 방이 크다.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>med_rag</t>
+          <t>wpn_silver_dagger</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>넝마</t>
+          <t>은 단검</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>잡화</t>
+          <t>한손 검</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>709</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>195</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>60</v>
+        <v>886.2</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>cloth x1</t>
+          <t>Res_SilverIngot x2 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>394</v>
       </c>
       <c r="N69" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4667,75 +4659,83 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>찢은 천 조각. 급한 대로 상처를 묶는다 — 없는 것보단 낫다.</t>
+          <t>짧고 빠르다. 은은 어둠에서 온 것을 태운다.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Crop_Wheat</t>
+          <t>arm_steel_head</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>밀</t>
+          <t>강철 투구</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>잡화</t>
+          <t>머리 방어구</t>
         </is>
       </c>
       <c r="D70" t="n">
+        <v>704</v>
+      </c>
+      <c r="E70" t="n">
+        <v>176</v>
+      </c>
+      <c r="F70" t="n">
         <v>4</v>
       </c>
-      <c r="E70" t="n">
-        <v>2</v>
-      </c>
-      <c r="F70" t="n">
-        <v>2</v>
-      </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="I70" t="n">
-        <v>13.3</v>
+        <v>220</v>
       </c>
       <c r="J70" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1x1</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Res_Steel x3 + leather x1</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>414</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1.7</v>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>빻아 빵을 굽는 곡물. 그대로는 먹기 어렵다.</t>
+          <t>머리를 지킨다. 기절 판정이 잦은 부위라 값어치가 크다.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>arm_steel_chest</t>
+          <t>Arm_IronChest</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>강철 흉갑</t>
+          <t>철 갑옷</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1256</v>
+        <v>669</v>
       </c>
       <c r="E71" t="n">
-        <v>314</v>
+        <v>167</v>
       </c>
       <c r="F71" t="n">
         <v>4</v>
@@ -4756,10 +4756,10 @@
         <v>0.5</v>
       </c>
       <c r="H71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I71" t="n">
-        <v>139.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>1</v>
@@ -4771,78 +4771,78 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Res_Steel x5 + leather x2</t>
+          <t>Res_Steel x3 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>698</v>
+        <v>398</v>
       </c>
       <c r="N71" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>무겁지만 확실하다. 급소를 통째로 덮는다.</t>
+          <t>철 갑옷.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Wpn_SteelSword</t>
+          <t>arm_hardleather_chest</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>강철 대검</t>
+          <t>질긴 가죽 갑옷</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>양손 검</t>
+          <t>몸통 방어구</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>992</v>
+        <v>630</v>
       </c>
       <c r="E72" t="n">
-        <v>273</v>
+        <v>158</v>
       </c>
       <c r="F72" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G72" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H72" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I72" t="n">
-        <v>198.4</v>
+        <v>140</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2x4</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Res_Steel x4 + Res_Lumber x2</t>
+          <t>res_hardleather x5</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>536</v>
+        <v>370</v>
       </c>
       <c r="N72" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -4851,31 +4851,31 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>강철 대검.</t>
+          <t>겹쳐 누빈 두꺼운 가죽. 강철 흉갑의 절반 무게로 그 절반보다 조금 더 막는다.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>wpn_steel_axe</t>
+          <t>wpn_arcane_staff</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>강철 도끼</t>
+          <t>비전 지팡이</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>양손 도끼</t>
+          <t>지팡이</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>710</v>
+        <v>612</v>
       </c>
       <c r="E73" t="n">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="F73" t="n">
         <v>3.6</v>
@@ -4884,29 +4884,29 @@
         <v>0.55</v>
       </c>
       <c r="H73" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>208.8</v>
+        <v>306</v>
       </c>
       <c r="J73" t="n">
         <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2x4</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + Res_Lumber x2</t>
+          <t>crystal_arcane x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>406</v>
+        <v>360</v>
       </c>
       <c r="N73" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -4915,31 +4915,31 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>무겁게 내리쳐 갑옷째 부순다. 느리지만 한 방이 크다.</t>
+          <t>**갑옷도 저항도 지나간다.** 대신 그리 아프지 않다.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>wpn_silver_dagger</t>
+          <t>wpn_dark_staff</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>은 단검</t>
+          <t>공허 지팡이</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>한손 검</t>
+          <t>지팡이</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>709</v>
+        <v>604</v>
       </c>
       <c r="E74" t="n">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="F74" t="n">
         <v>3.6</v>
@@ -4948,29 +4948,29 @@
         <v>0.55</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>886.2</v>
+        <v>302</v>
       </c>
       <c r="J74" t="n">
         <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Res_SilverIngot x2 + Res_Lumber x1</t>
+          <t>crystal_dark x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>394</v>
+        <v>356</v>
       </c>
       <c r="N74" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -4979,59 +4979,59 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>짧고 빠르다. 은은 어둠에서 온 것을 태운다.</t>
+          <t>상처를 아물지 못하게 하고 부패를 쌓는다.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>arm_steel_head</t>
+          <t>wpn_holy_staff</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>강철 투구</t>
+          <t>성광 지팡이</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>머리 방어구</t>
+          <t>지팡이</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>704</v>
+        <v>598</v>
       </c>
       <c r="E75" t="n">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H75" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>220</v>
+        <v>299</v>
       </c>
       <c r="J75" t="n">
         <v>1</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + leather x1</t>
+          <t>crystal_holy x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>414</v>
+        <v>352</v>
       </c>
       <c r="N75" t="n">
         <v>1.7</v>
@@ -5043,126 +5043,126 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>머리를 지킨다. 기절 판정이 잦은 부위라 값어치가 크다.</t>
+          <t>**언데드에게 두 배.** 휘두른 사람을 추스른다.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Arm_IronChest</t>
+          <t>wpn_lightning_staff</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>철 갑옷</t>
+          <t>뇌전 지팡이</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>몸통 방어구</t>
+          <t>지팡이</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>669</v>
+        <v>587</v>
       </c>
       <c r="E76" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F76" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H76" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>83.59999999999999</v>
+        <v>293.5</v>
       </c>
       <c r="J76" t="n">
         <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + Res_Lumber x1</t>
+          <t>crystal_lightning x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>398</v>
+        <v>346</v>
       </c>
       <c r="N76" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>철 갑옷.</t>
+          <t>몸을 굳힌다 — 공격이 느려진다. 젖은 상대에게 1.5배.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>arm_hardleather_chest</t>
+          <t>wpn_fire_staff</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>질긴 가죽 갑옷</t>
+          <t>화염 지팡이</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>몸통 방어구</t>
+          <t>지팡이</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>630</v>
+        <v>572</v>
       </c>
       <c r="E77" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H77" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
-        <v>140</v>
+        <v>286</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>res_hardleather x5</t>
+          <t>crystal_fire x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="N77" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -5171,19 +5171,19 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>겹쳐 누빈 두꺼운 가죽. 강철 흉갑의 절반 무게로 그 절반보다 조금 더 막는다.</t>
+          <t>닿은 것을 태운다. 화상이 남는다.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>wpn_storm_staff</t>
+          <t>wpn_earth_staff</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>뇌전 지팡이</t>
+          <t>지반 지팡이</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="E78" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F78" t="n">
         <v>3.6</v>
@@ -5204,10 +5204,10 @@
         <v>0.55</v>
       </c>
       <c r="H78" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>279.5</v>
+        <v>283</v>
       </c>
       <c r="J78" t="n">
         <v>1</v>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>crystal_elemental_lightning x1 + Res_Lumber x3</t>
+          <t>crystal_earth x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="N78" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -5235,19 +5235,19 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>번개 결정을 물린 지팡이. 사거리가 가장 길고, 맞은 것을 잠시 굳힌다.</t>
+          <t>발밑을 흔들어 **넘어뜨린다**(기절 굴림 보정).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>wpn_flame_staff</t>
+          <t>wpn_water_staff</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>화염 지팡이</t>
+          <t>해류 지팡이</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>572</v>
+        <v>548</v>
       </c>
       <c r="E79" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F79" t="n">
         <v>3.6</v>
@@ -5271,7 +5271,7 @@
         <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="J79" t="n">
         <v>1</v>
@@ -5283,14 +5283,14 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>crystal_elemental_fire x1 + Res_Lumber x3</t>
+          <t>crystal_water x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="N79" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -5299,31 +5299,31 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>원소 화염 결정을 물린 지팡이. 닿은 것을 태운다.</t>
+          <t>적을 적신다 — 느려지고, **다음 번개가 1.5배로 아프다**.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>wpn_frost_staff</t>
+          <t>wpn_steel_spear</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>냉기 지팡이</t>
+          <t>강철 창</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>지팡이</t>
+          <t>장병기</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>572</v>
+        <v>483</v>
       </c>
       <c r="E80" t="n">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="F80" t="n">
         <v>3.6</v>
@@ -5332,10 +5332,10 @@
         <v>0.55</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="I80" t="n">
-        <v>286</v>
+        <v>185.8</v>
       </c>
       <c r="J80" t="n">
         <v>1</v>
@@ -5347,14 +5347,14 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>crystal_elemental_ice x1 + Res_Lumber x3</t>
+          <t>Res_Steel x2 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="N80" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -5363,31 +5363,31 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>얼려 굳힌다. 화염보다 덜 아프지만 더 오래 붙든다.</t>
+          <t>먼저 닿는다. 거리를 유지하며 찌른다.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>wpn_venom_staff</t>
+          <t>Wpn_BronzeSword</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>맹독 지팡이</t>
+          <t>청동검</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>지팡이</t>
+          <t>한손 검</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>557</v>
+        <v>450</v>
       </c>
       <c r="E81" t="n">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="F81" t="n">
         <v>3.6</v>
@@ -5396,29 +5396,29 @@
         <v>0.55</v>
       </c>
       <c r="H81" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="I81" t="n">
-        <v>309.4</v>
+        <v>180</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>crystal_elemental_poison x1 + Res_Lumber x2</t>
+          <t>Res_Bronze x3 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="N81" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -5427,31 +5427,31 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>약하게 자주 맞힌다. 한 방보다 시간이 죽인다.</t>
+          <t>청동검.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>wpn_steel_spear</t>
+          <t>Wpn_Crossbow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>강철 창</t>
+          <t>석궁</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>장병기</t>
+          <t>쇠뇌</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>483</v>
+        <v>200</v>
       </c>
       <c r="E82" t="n">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="F82" t="n">
         <v>3.6</v>
@@ -5460,29 +5460,29 @@
         <v>0.55</v>
       </c>
       <c r="H82" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="I82" t="n">
-        <v>185.8</v>
+        <v>66.7</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Res_Steel x2 + Res_Lumber x3</t>
+          <t>Res_Lumber x4 + Res_IronOre x2 + rope x1</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>284</v>
+        <v>114</v>
       </c>
       <c r="N82" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5491,62 +5491,62 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>먼저 닿는다. 거리를 유지하며 찌른다.</t>
+          <t>석궁.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Wpn_BronzeSword</t>
+          <t>Arm_LeatherChest</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>청동검</t>
+          <t>가죽 갑옷</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>한손 검</t>
+          <t>몸통 방어구</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>450</v>
+        <v>194</v>
       </c>
       <c r="E83" t="n">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="F83" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G83" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H83" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I83" t="n">
-        <v>180</v>
+        <v>64.7</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Res_Bronze x3 + Res_Lumber x1</t>
+          <t>leather x5</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>281</v>
+        <v>120</v>
       </c>
       <c r="N83" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -5555,43 +5555,43 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>청동검.</t>
+          <t>가죽 갑옷.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Wpn_Crossbow</t>
+          <t>Arm_IronLegs</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>석궁</t>
+          <t>철 각반</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>쇠뇌</t>
+          <t>다리 방어구</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="E84" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F84" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G84" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H84" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="I84" t="n">
-        <v>66.7</v>
+        <v>39.8</v>
       </c>
       <c r="J84" t="n">
         <v>1</v>
@@ -5603,14 +5603,14 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Res_Lumber x4 + Res_IronOre x2 + rope x1</t>
+          <t>Res_IronOre x4 + leather x1</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="N84" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5619,62 +5619,62 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>석궁.</t>
+          <t>철 각반.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Arm_LeatherChest</t>
+          <t>Wpn_IronShield</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>가죽 갑옷</t>
+          <t>철 방패</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>몸통 방어구</t>
+          <t>방패</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="E85" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F85" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G85" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H85" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="I85" t="n">
-        <v>64.7</v>
+        <v>108.7</v>
       </c>
       <c r="J85" t="n">
         <v>1</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>leather x5</t>
+          <t>Res_IronOre x4 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="N85" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -5683,62 +5683,62 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>가죽 갑옷.</t>
+          <t>철 방패.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Arm_IronLegs</t>
+          <t>Wpn_IronMace</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>철 각반</t>
+          <t>철 철퇴</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>다리 방어구</t>
+          <t>한손 둔기</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="E86" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="G86" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H86" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I86" t="n">
-        <v>39.8</v>
+        <v>42.9</v>
       </c>
       <c r="J86" t="n">
         <v>1</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + leather x1</t>
+          <t>Res_IronOre x4 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="N86" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -5747,31 +5747,31 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>철 각반.</t>
+          <t>철 철퇴.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Wpn_IronShield</t>
+          <t>Wpn_IronSword</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>철 방패</t>
+          <t>철검</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>방패</t>
+          <t>한손 검</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="E87" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F87" t="n">
         <v>3.6</v>
@@ -5780,90 +5780,90 @@
         <v>0.55</v>
       </c>
       <c r="H87" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>108.7</v>
+        <v>48</v>
       </c>
       <c r="J87" t="n">
         <v>1</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x2</t>
+          <t>Res_IronOre x4 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="N87" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>철 방패.</t>
+          <t>철검.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Wpn_IronMace</t>
+          <t>Arm_IronHands</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>철 철퇴</t>
+          <t>철 건틀릿</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>한손 둔기</t>
+          <t>손 방어구</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E88" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F88" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G88" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H88" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>42.9</v>
+        <v>71.5</v>
       </c>
       <c r="J88" t="n">
         <v>1</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x1</t>
+          <t>Res_IronOre x3 + leather x1</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="N88" t="n">
         <v>1.7</v>
@@ -5875,43 +5875,43 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>철 철퇴.</t>
+          <t>철 건틀릿.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Wpn_IronSword</t>
+          <t>Wpn_IronAxe</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>철검</t>
+          <t>철도끼</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>한손 검</t>
+          <t>한손 도끼</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="E89" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F89" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G89" t="n">
         <v>0.55</v>
       </c>
       <c r="H89" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I89" t="n">
-        <v>48</v>
+        <v>36.9</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -5923,78 +5923,78 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x1</t>
+          <t>Res_IronOre x3 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="N89" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>철검.</t>
+          <t>철도끼.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Arm_IronHands</t>
+          <t>wpn_longbow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>철 건틀릿</t>
+          <t>장궁</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>손 방어구</t>
+          <t>활</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="E90" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F90" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G90" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="I90" t="n">
-        <v>71.5</v>
+        <v>76.2</v>
       </c>
       <c r="J90" t="n">
         <v>1</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Res_IronOre x3 + leather x1</t>
+          <t>Res_Lumber x4 + rope x1</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="N90" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -6003,31 +6003,31 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>철 건틀릿.</t>
+          <t>당기는 힘이 곧 사거리다. 숙련자만 제 성능을 낸다.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Wpn_IronAxe</t>
+          <t>Wpn_Spear</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>철도끼</t>
+          <t>장창</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>한손 도끼</t>
+          <t>장병기</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E91" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F91" t="n">
         <v>3.7</v>
@@ -6036,29 +6036,29 @@
         <v>0.55</v>
       </c>
       <c r="H91" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I91" t="n">
-        <v>36.9</v>
+        <v>29.5</v>
       </c>
       <c r="J91" t="n">
         <v>1</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Res_IronOre x3 + Res_Lumber x2</t>
+          <t>Res_IronOre x2 + Res_Lumber x4</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N91" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -6067,62 +6067,62 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>철도끼.</t>
+          <t>장창.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>wpn_longbow</t>
+          <t>Arm_LeatherLegs</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>장궁</t>
+          <t>가죽 각반</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>활</t>
+          <t>다리 방어구</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E92" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F92" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="G92" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H92" t="n">
         <v>1.6</v>
       </c>
       <c r="I92" t="n">
-        <v>76.2</v>
+        <v>71.2</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Res_Lumber x4 + rope x1</t>
+          <t>leather x3</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N92" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -6131,31 +6131,31 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>당기는 힘이 곧 사거리다. 숙련자만 제 성능을 낸다.</t>
+          <t>가죽 각반.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Wpn_Spear</t>
+          <t>Wpn_ShortBow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>장창</t>
+          <t>단궁</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>장병기</t>
+          <t>활</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E93" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F93" t="n">
         <v>3.7</v>
@@ -6164,29 +6164,29 @@
         <v>0.55</v>
       </c>
       <c r="H93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>29.5</v>
+        <v>53</v>
       </c>
       <c r="J93" t="n">
         <v>1</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Res_IronOre x2 + Res_Lumber x4</t>
+          <t>Res_Lumber x3 + rope x1</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="N93" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -6195,43 +6195,43 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>장창.</t>
+          <t>단궁.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Arm_LeatherLegs</t>
+          <t>Arm_IronHead</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>가죽 각반</t>
+          <t>철 투구</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>다리 방어구</t>
+          <t>머리 방어구</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E94" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F94" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="G94" t="n">
         <v>0.5</v>
       </c>
       <c r="H94" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="I94" t="n">
-        <v>71.2</v>
+        <v>34</v>
       </c>
       <c r="J94" t="n">
         <v>1</v>
@@ -6243,14 +6243,14 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>leather x3</t>
+          <t>Res_IronOre x3</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="N94" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -6259,43 +6259,43 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>가죽 각반.</t>
+          <t>철 투구.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Wpn_ShortBow</t>
+          <t>arm_cloth_chest</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>단궁</t>
+          <t>천 옷</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>활</t>
+          <t>몸통 방어구</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E95" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F95" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G95" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="J95" t="n">
         <v>1</v>
@@ -6307,14 +6307,14 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Res_Lumber x3 + rope x1</t>
+          <t>cloth x4</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="N95" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -6323,62 +6323,62 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>단궁.</t>
+          <t>거의 막지 못하지만 아무것도 안 입는 것보단 낫다. 가볍다.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Arm_IronHead</t>
+          <t>Arm_LeatherHands</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>철 투구</t>
+          <t>가죽 장갑</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>머리 방어구</t>
+          <t>손 방어구</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="E96" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F96" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="G96" t="n">
         <v>0.5</v>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="I96" t="n">
-        <v>34</v>
+        <v>92.5</v>
       </c>
       <c r="J96" t="n">
         <v>1</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Res_IronOre x3</t>
+          <t>leather x2</t>
         </is>
       </c>
       <c r="M96" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N96" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -6387,62 +6387,62 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>철 투구.</t>
+          <t>가죽 장갑.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>arm_cloth_chest</t>
+          <t>Arm_LeatherHead</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>천 옷</t>
+          <t>가죽 모자</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>몸통 방어구</t>
+          <t>머리 방어구</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E97" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F97" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G97" t="n">
         <v>0.5</v>
       </c>
       <c r="H97" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I97" t="n">
-        <v>105</v>
+        <v>61.7</v>
       </c>
       <c r="J97" t="n">
         <v>1</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>cloth x4</t>
+          <t>leather x2</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="N97" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6451,62 +6451,62 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>거의 막지 못하지만 아무것도 안 입는 것보단 낫다. 가볍다.</t>
+          <t>가죽 모자.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Arm_LeatherHands</t>
+          <t>Wpn_WoodShield</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>가죽 장갑</t>
+          <t>나무 방패</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>손 방어구</t>
+          <t>방패</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="E98" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F98" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="G98" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H98" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>92.5</v>
+        <v>50</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>leather x2</t>
+          <t>Res_Lumber x4</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="N98" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6515,62 +6515,62 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>가죽 장갑.</t>
+          <t>나무 방패.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Arm_LeatherHead</t>
+          <t>wpn_bone_club</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>가죽 모자</t>
+          <t>뼈 몽둥이</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>머리 방어구</t>
+          <t>한손 둔기</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E99" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F99" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="G99" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H99" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="I99" t="n">
-        <v>61.7</v>
+        <v>19.2</v>
       </c>
       <c r="J99" t="n">
         <v>1</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>leather x2</t>
+          <t>res_bone x4 + leather x1</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="N99" t="n">
-        <v>1.54</v>
+        <v>0.82</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6579,146 +6579,18 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>가죽 모자.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Wpn_WoodShield</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>나무 방패</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>방패</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>50</v>
-      </c>
-      <c r="E100" t="n">
-        <v>14</v>
-      </c>
-      <c r="F100" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H100" t="n">
-        <v>1</v>
-      </c>
-      <c r="I100" t="n">
-        <v>50</v>
-      </c>
-      <c r="J100" t="n">
-        <v>1</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>2x2</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Res_Lumber x4</t>
-        </is>
-      </c>
-      <c r="M100" t="n">
-        <v>32</v>
-      </c>
-      <c r="N100" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>나무 방패.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>wpn_bone_club</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>뼈 몽둥이</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>한손 둔기</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>46</v>
-      </c>
-      <c r="E101" t="n">
-        <v>13</v>
-      </c>
-      <c r="F101" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H101" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I101" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="J101" t="n">
-        <v>1</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>1x3</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>res_bone x4 + leather x1</t>
-        </is>
-      </c>
-      <c r="M101" t="n">
-        <v>56</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
           <t>굵은 다리뼈를 가죽으로 감아 쥔 것. 잘 들지는 않아도 잘 부러뜨린다 — 죽이기보다 눕히기에 낫다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P101"/>
-  <conditionalFormatting sqref="N2:N101">
+  <autoFilter ref="A1:P99"/>
+  <conditionalFormatting sqref="N2:N99">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D101">
+  <conditionalFormatting sqref="D2:D99">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6738,7 +6610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8220,17 +8092,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gem_elemental_fire</t>
+          <t>gem_arcane</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>원소 화염 결정 제작</t>
+          <t>비전 결정 제작</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>crystal_elemental_fire</t>
+          <t>crystal_arcane</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -8238,17 +8110,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Res_Ruby x1 + Res_MagicStone x1</t>
+          <t>Res_MagicStone x2</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="G28" t="n">
-        <v>285</v>
+        <v>336</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -8271,17 +8143,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gem_elemental_ice</t>
+          <t>gem_dark</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>원소 냉기 결정 제작</t>
+          <t>공허 결정 제작</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>crystal_elemental_ice</t>
+          <t>crystal_dark</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -8289,17 +8161,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Res_Sapphire x1 + Res_MagicStone x1</t>
+          <t>Res_Voidstone x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="G29" t="n">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -8322,17 +8194,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gem_elemental_lightning</t>
+          <t>gem_earth</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>원소 번개 결정 제작</t>
+          <t>지반 결정 제작</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>crystal_elemental_lightning</t>
+          <t>crystal_earth</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -8340,17 +8212,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Res_Topaz x1 + Res_MagicStone x1</t>
+          <t>Res_Emerald x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>190</v>
       </c>
       <c r="G30" t="n">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -8373,17 +8245,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gem_elemental_poison</t>
+          <t>gem_fire</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>원소 독 결정 제작</t>
+          <t>화염 결정 제작</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>crystal_elemental_poison</t>
+          <t>crystal_fire</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -8391,17 +8263,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Res_Emerald x1 + Res_MagicStone x1</t>
+          <t>Res_Ruby x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>190</v>
       </c>
       <c r="G31" t="n">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="H31" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -8424,17 +8296,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gem_dark_fire</t>
+          <t>gem_holy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>암흑 화염 결정 제작</t>
+          <t>성광 결정 제작</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>crystal_dark_fire</t>
+          <t>crystal_holy</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -8442,17 +8314,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Res_Ruby x1 + Res_Voidstone x1</t>
+          <t>Res_Etherstone x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="G32" t="n">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -8460,10 +8332,10 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
@@ -8475,17 +8347,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>gem_dark_ice</t>
+          <t>gem_lightning</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>암흑 냉기 결정 제작</t>
+          <t>뇌전 결정 제작</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>crystal_dark_ice</t>
+          <t>crystal_lightning</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -8493,17 +8365,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Res_Sapphire x1 + Res_Voidstone x1</t>
+          <t>Res_Topaz x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G33" t="n">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="H33" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -8511,10 +8383,10 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
@@ -8526,17 +8398,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gem_dark_lightning</t>
+          <t>gem_water</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>암흑 번개 결정 제작</t>
+          <t>해류 결정 제작</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>crystal_dark_lightning</t>
+          <t>crystal_water</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -8544,17 +8416,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Res_Topaz x1 + Res_Voidstone x1</t>
+          <t>Res_Sapphire x1 + Res_MagicStone x1</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G34" t="n">
-        <v>357</v>
+        <v>301</v>
       </c>
       <c r="H34" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -8562,10 +8434,10 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
@@ -8577,46 +8449,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gem_dark_poison</t>
+          <t>craft_bandage</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>암흑 독 결정 제작</t>
+          <t>붕대 만들기</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>crystal_dark_poison</t>
+          <t>med_bandage</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Res_Emerald x1 + Res_Voidstone x1</t>
+          <t>cloth x2</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="G35" t="n">
-        <v>357</v>
+        <v>44</v>
       </c>
       <c r="H35" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
@@ -8628,46 +8500,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gem_holy_fire</t>
+          <t>craft_cloth</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>신성 화염 결정 제작</t>
+          <t>천 짜기</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>crystal_holy_fire</t>
+          <t>cloth</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Res_Ruby x1 + Res_Etherstone x1</t>
+          <t>herbs x3</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="G36" t="n">
-        <v>357</v>
+        <v>28</v>
       </c>
       <c r="H36" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
@@ -8679,17 +8551,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>gem_holy_ice</t>
+          <t>craft_leather</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>신성 냉기 결정 제작</t>
+          <t>가죽 무두질</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>crystal_holy_ice</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -8697,28 +8569,28 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Res_Sapphire x1 + Res_Etherstone x1</t>
+          <t>res_rawhide x2</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="G37" t="n">
-        <v>357</v>
+        <v>24</v>
       </c>
       <c r="H37" t="n">
-        <v>1.7</v>
+        <v>1.09</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
@@ -8730,46 +8602,46 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>gem_holy_lightning</t>
+          <t>craft_rag</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>신성 번개 결정 제작</t>
+          <t>넝마 찢기</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>crystal_holy_lightning</t>
+          <t>med_rag</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Res_Topaz x1 + Res_Etherstone x1</t>
+          <t>cloth x1</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="G38" t="n">
-        <v>357</v>
+        <v>18</v>
       </c>
       <c r="H38" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
@@ -8781,17 +8653,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gem_holy_poison</t>
+          <t>craft_rope</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>신성 독 결정 제작</t>
+          <t>밧줄 꼬기</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>crystal_holy_poison</t>
+          <t>rope</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -8799,28 +8671,28 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Res_Emerald x1 + Res_Etherstone x1</t>
+          <t>cloth x2</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="G39" t="n">
-        <v>357</v>
+        <v>42</v>
       </c>
       <c r="H39" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Gemcutting</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
@@ -8832,35 +8704,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>craft_bandage</t>
+          <t>craft_wood_shield</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>붕대 만들기</t>
+          <t>나무 방패 제작</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>med_bandage</t>
+          <t>Wpn_WoodShield</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>cloth x2</t>
+          <t>Res_Lumber x4</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G40" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H40" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -8868,10 +8740,10 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
@@ -8883,35 +8755,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>craft_cloth</t>
+          <t>craft_short_bow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>천 짜기</t>
+          <t>단궁 제작</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>cloth</t>
+          <t>Wpn_ShortBow</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>herbs x3</t>
+          <t>Res_Lumber x3 + rope x1</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="G41" t="n">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="H41" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -8919,10 +8791,10 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
@@ -8934,17 +8806,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>craft_leather</t>
+          <t>craft_longbow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>가죽 무두질</t>
+          <t>장궁 제작</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>wpn_longbow</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -8952,17 +8824,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>res_rawhide x2</t>
+          <t>Res_Lumber x4 + rope x1</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="G42" t="n">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="H42" t="n">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -8970,12 +8842,16 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Res_WeaponSmithing</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -8985,46 +8861,46 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>craft_rag</t>
+          <t>craft_hardleather</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>넝마 찢기</t>
+          <t>두꺼운 가죽 무두질</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>med_rag</t>
+          <t>res_hardleather</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>cloth x1</t>
+          <t>res_thickhide x2</t>
         </is>
       </c>
       <c r="F43" t="n">
+        <v>68</v>
+      </c>
+      <c r="G43" t="n">
+        <v>74</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>20</v>
+      </c>
+      <c r="K43" t="n">
         <v>14</v>
-      </c>
-      <c r="G43" t="n">
-        <v>18</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
@@ -9036,17 +8912,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>craft_rope</t>
+          <t>craft_bone_club</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>밧줄 꼬기</t>
+          <t>뼈 몽둥이 제작</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rope</t>
+          <t>wpn_bone_club</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -9054,30 +8930,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>cloth x2</t>
+          <t>res_bone x4 + leather x1</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="G44" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5</v>
+        <v>0.82</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>WeaponCrafting</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Res_Bonecraft</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -9087,17 +8967,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>craft_wood_shield</t>
+          <t>craft_bronze_sword</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>나무 방패 제작</t>
+          <t>청동검 제작</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wpn_WoodShield</t>
+          <t>Wpn_BronzeSword</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -9105,30 +8985,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Res_Lumber x4</t>
+          <t>Res_Bronze x3 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>32</v>
+        <v>281</v>
       </c>
       <c r="G45" t="n">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="H45" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>WeaponCrafting</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>8</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Res_Smelting</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -9138,17 +9022,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>craft_short_bow</t>
+          <t>craft_spear</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>단궁 제작</t>
+          <t>장창 제작</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wpn_ShortBow</t>
+          <t>Wpn_Spear</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -9156,25 +9040,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Res_Lumber x3 + rope x1</t>
+          <t>Res_IronOre x2 + Res_Lumber x4</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G46" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H46" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>WeaponCrafting</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K46" t="n">
         <v>12</v>
@@ -9189,17 +9073,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>craft_longbow</t>
+          <t>craft_iron_axe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>장궁 제작</t>
+          <t>철도끼 제작</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>wpn_longbow</t>
+          <t>Wpn_IronAxe</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -9207,28 +9091,28 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Res_Lumber x4 + rope x1</t>
+          <t>Res_IronOre x3 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G47" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H47" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>WeaponCrafting</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -9244,17 +9128,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>craft_hardleather</t>
+          <t>craft_iron_mace</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>두꺼운 가죽 무두질</t>
+          <t>철 철퇴 제작</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>res_hardleather</t>
+          <t>Wpn_IronMace</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -9262,21 +9146,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>res_thickhide x2</t>
+          <t>Res_IronOre x4 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="G48" t="n">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="H48" t="n">
-        <v>1.09</v>
+        <v>1.7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>WeaponCrafting</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -9285,7 +9169,11 @@
       <c r="K48" t="n">
         <v>14</v>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Res_WeaponSmithing</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -9295,17 +9183,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>craft_bone_club</t>
+          <t>craft_steel_spear</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>뼈 몽둥이 제작</t>
+          <t>강철 창 제작</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>wpn_bone_club</t>
+          <t>wpn_steel_spear</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -9313,17 +9201,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>res_bone x4 + leather x1</t>
+          <t>Res_Steel x2 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>56</v>
+        <v>284</v>
       </c>
       <c r="G49" t="n">
-        <v>46</v>
+        <v>483</v>
       </c>
       <c r="H49" t="n">
-        <v>0.82</v>
+        <v>1.7</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -9331,14 +9219,14 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Res_Bonecraft</t>
+          <t>Res_WeaponSmithing</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -9350,17 +9238,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>craft_bronze_sword</t>
+          <t>craft_crossbow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>청동검 제작</t>
+          <t>석궁 제작</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wpn_BronzeSword</t>
+          <t>Wpn_Crossbow</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -9368,17 +9256,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Res_Bronze x3 + Res_Lumber x1</t>
+          <t>Res_Lumber x4 + Res_IronOre x2 + rope x1</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>281</v>
+        <v>114</v>
       </c>
       <c r="G50" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H50" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -9386,14 +9274,14 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K50" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Res_Smelting</t>
+          <t>Res_WeaponSmithing</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -9405,17 +9293,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>craft_spear</t>
+          <t>craft_steel_axe</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>장창 제작</t>
+          <t>강철 도끼 제작</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wpn_Spear</t>
+          <t>wpn_steel_axe</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -9423,17 +9311,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Res_IronOre x2 + Res_Lumber x4</t>
+          <t>Res_Steel x3 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>72</v>
+        <v>406</v>
       </c>
       <c r="G51" t="n">
-        <v>118</v>
+        <v>710</v>
       </c>
       <c r="H51" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -9441,12 +9329,16 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>12</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Res_WeaponSmithing</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>JSON</t>
@@ -9456,17 +9348,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>craft_iron_axe</t>
+          <t>craft_silver_dagger</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>철도끼 제작</t>
+          <t>은 단검 제작</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wpn_IronAxe</t>
+          <t>wpn_silver_dagger</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -9474,17 +9366,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Res_IronOre x3 + Res_Lumber x2</t>
+          <t>Res_SilverIngot x2 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>76</v>
+        <v>394</v>
       </c>
       <c r="G52" t="n">
-        <v>129</v>
+        <v>709</v>
       </c>
       <c r="H52" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -9492,10 +9384,10 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K52" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -9511,17 +9403,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>craft_iron_mace</t>
+          <t>craft_arcane_staff</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>철 철퇴 제작</t>
+          <t>비전 지팡이 제작</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wpn_IronMace</t>
+          <t>wpn_arcane_staff</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -9529,14 +9421,14 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x1</t>
+          <t>crystal_arcane x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>88</v>
+        <v>360</v>
       </c>
       <c r="G53" t="n">
-        <v>150</v>
+        <v>612</v>
       </c>
       <c r="H53" t="n">
         <v>1.7</v>
@@ -9547,14 +9439,14 @@
         </is>
       </c>
       <c r="J53" t="n">
+        <v>35</v>
+      </c>
+      <c r="K53" t="n">
         <v>20</v>
       </c>
-      <c r="K53" t="n">
-        <v>14</v>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Res_WeaponSmithing</t>
+          <t>Res_ElementalCraft</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -9566,17 +9458,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>craft_steel_spear</t>
+          <t>craft_dark_staff</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>강철 창 제작</t>
+          <t>공허 지팡이 제작</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>wpn_steel_spear</t>
+          <t>wpn_dark_staff</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -9584,14 +9476,14 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Res_Steel x2 + Res_Lumber x3</t>
+          <t>crystal_dark x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="G54" t="n">
-        <v>483</v>
+        <v>604</v>
       </c>
       <c r="H54" t="n">
         <v>1.7</v>
@@ -9602,14 +9494,14 @@
         </is>
       </c>
       <c r="J54" t="n">
+        <v>35</v>
+      </c>
+      <c r="K54" t="n">
         <v>20</v>
       </c>
-      <c r="K54" t="n">
-        <v>14</v>
-      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Res_WeaponSmithing</t>
+          <t>Res_ElementalCraft</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -9621,17 +9513,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>craft_crossbow</t>
+          <t>craft_earth_staff</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>석궁 제작</t>
+          <t>지반 지팡이 제작</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wpn_Crossbow</t>
+          <t>wpn_earth_staff</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -9639,17 +9531,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Res_Lumber x4 + Res_IronOre x2 + rope x1</t>
+          <t>crystal_earth x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>114</v>
+        <v>335</v>
       </c>
       <c r="G55" t="n">
-        <v>200</v>
+        <v>566</v>
       </c>
       <c r="H55" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -9657,14 +9549,14 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K55" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Res_WeaponSmithing</t>
+          <t>Res_ElementalCraft</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -9676,17 +9568,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>craft_steel_axe</t>
+          <t>craft_fire_staff</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>강철 도끼 제작</t>
+          <t>화염 지팡이 제작</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>wpn_steel_axe</t>
+          <t>wpn_fire_staff</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -9694,17 +9586,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + Res_Lumber x2</t>
+          <t>crystal_fire x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>406</v>
+        <v>338</v>
       </c>
       <c r="G56" t="n">
-        <v>710</v>
+        <v>572</v>
       </c>
       <c r="H56" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -9712,14 +9604,14 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Res_WeaponSmithing</t>
+          <t>Res_ElementalCraft</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -9731,17 +9623,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>craft_silver_dagger</t>
+          <t>craft_holy_staff</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>은 단검 제작</t>
+          <t>성광 지팡이 제작</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wpn_silver_dagger</t>
+          <t>wpn_holy_staff</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -9749,17 +9641,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Res_SilverIngot x2 + Res_Lumber x1</t>
+          <t>crystal_holy x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>394</v>
+        <v>352</v>
       </c>
       <c r="G57" t="n">
-        <v>709</v>
+        <v>598</v>
       </c>
       <c r="H57" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -9767,14 +9659,14 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K57" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Res_WeaponSmithing</t>
+          <t>Res_ElementalCraft</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -9786,17 +9678,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>craft_flame_staff</t>
+          <t>craft_lightning_staff</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>화염 지팡이 제작</t>
+          <t>뇌전 지팡이 제작</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>wpn_flame_staff</t>
+          <t>wpn_lightning_staff</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -9804,17 +9696,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>crystal_elemental_fire x1 + Res_Lumber x3</t>
+          <t>crystal_lightning x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="G58" t="n">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="H58" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -9841,17 +9733,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>craft_frost_staff</t>
+          <t>craft_steel_sword</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>냉기 지팡이 제작</t>
+          <t>강철 대검 제작</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wpn_frost_staff</t>
+          <t>Wpn_SteelSword</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -9859,14 +9751,14 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>crystal_elemental_ice x1 + Res_Lumber x3</t>
+          <t>Res_Steel x4 + Res_Lumber x2</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>309</v>
+        <v>536</v>
       </c>
       <c r="G59" t="n">
-        <v>572</v>
+        <v>992</v>
       </c>
       <c r="H59" t="n">
         <v>1.85</v>
@@ -9884,7 +9776,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Res_ElementalCraft</t>
+          <t>Res_Steelmaking</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -9896,17 +9788,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>craft_steel_sword</t>
+          <t>craft_water_staff</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>강철 대검 제작</t>
+          <t>해류 지팡이 제작</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wpn_SteelSword</t>
+          <t>wpn_water_staff</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -9914,17 +9806,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Res_Steel x4 + Res_Lumber x2</t>
+          <t>crystal_water x1 + Res_Lumber x3</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>536</v>
+        <v>325</v>
       </c>
       <c r="G60" t="n">
-        <v>992</v>
+        <v>548</v>
       </c>
       <c r="H60" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -9939,7 +9831,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Res_Steelmaking</t>
+          <t>Res_ElementalCraft</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -9951,72 +9843,68 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>craft_venom_staff</t>
+          <t>Rec_Lumber</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>맹독 지팡이 제작</t>
+          <t>판자</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>wpn_venom_staff</t>
+          <t>Res_Lumber</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>crystal_elemental_poison x1 + Res_Lumber x2</t>
+          <t>Res_Wood x3</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>301</v>
+        <v>9</v>
       </c>
       <c r="G61" t="n">
-        <v>557</v>
+        <v>16</v>
       </c>
       <c r="H61" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>WeaponCrafting</t>
+          <t>목공</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>18</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Res_ElementalCraft</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>SO</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>craft_storm_staff</t>
+          <t>Rec_IronSword</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>뇌전 지팡이 제작</t>
+          <t>철검</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>wpn_storm_staff</t>
+          <t>Wpn_IronSword</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -10024,83 +9912,79 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>crystal_elemental_lightning x1 + Res_Lumber x3</t>
+          <t>Res_IronOre x4 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>309</v>
+        <v>88</v>
       </c>
       <c r="G62" t="n">
-        <v>587</v>
+        <v>144</v>
       </c>
       <c r="H62" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>WeaponCrafting</t>
+          <t>무기제작</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="K62" t="n">
-        <v>22</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Res_ElementalCraft</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>SO</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rec_Lumber</t>
+          <t>Rec_IronChest</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>판자</t>
+          <t>철 갑옷</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Res_Lumber</t>
+          <t>Arm_IronChest</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Res_Wood x3</t>
+          <t>Res_Steel x3 + Res_Lumber x1</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>9</v>
+        <v>398</v>
       </c>
       <c r="G63" t="n">
-        <v>16</v>
+        <v>669</v>
       </c>
       <c r="H63" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>목공</t>
+          <t>방어구제작</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K63" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
@@ -10112,17 +9996,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rec_IronSword</t>
+          <t>Rec_CutStone</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>철검</t>
+          <t>다듬은 돌</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wpn_IronSword</t>
+          <t>Res_CutStone</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -10130,28 +10014,28 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Res_IronOre x4 + Res_Lumber x1</t>
+          <t>Res_Stone x2</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="G64" t="n">
-        <v>144</v>
+        <v>6</v>
       </c>
       <c r="H64" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>무기제작</t>
+          <t>석공</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K64" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
@@ -10163,46 +10047,46 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Rec_IronChest</t>
+          <t>Rec_Bread</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>철 갑옷</t>
+          <t>빵</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Arm_IronChest</t>
+          <t>Food_Bread</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Res_Steel x3 + Res_Lumber x1</t>
+          <t>Crop_Wheat x3</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>398</v>
+        <v>12</v>
       </c>
       <c r="G65" t="n">
-        <v>669</v>
+        <v>18</v>
       </c>
       <c r="H65" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>방어구제작</t>
+          <t>요리</t>
         </is>
       </c>
       <c r="J65" t="n">
+        <v>3</v>
+      </c>
+      <c r="K65" t="n">
         <v>18</v>
-      </c>
-      <c r="K65" t="n">
-        <v>120</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
@@ -10214,17 +10098,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Rec_CutStone</t>
+          <t>Rec_CookedMeat</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>다듬은 돌</t>
+          <t>구운 고기</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Res_CutStone</t>
+          <t>Food_CookedMeat</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -10232,25 +10116,25 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Res_Stone x2</t>
+          <t>Food_RawMeat x1</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H66" t="n">
         <v>1.5</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>석공</t>
+          <t>요리</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
         <v>15</v>
@@ -10265,46 +10149,46 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Rec_Bread</t>
+          <t>Rec_Bronze</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>빵</t>
+          <t>청동 주괴</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Food_Bread</t>
+          <t>Res_Bronze</t>
         </is>
       </c>
       <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Res_CopperOre x3 + Res_TinOre x1 + Res_Coal x1</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>60</v>
+      </c>
+      <c r="G67" t="n">
+        <v>91</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>제련</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
         <v>2</v>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Crop_Wheat x3</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>12</v>
-      </c>
-      <c r="G67" t="n">
-        <v>18</v>
-      </c>
-      <c r="H67" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>요리</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>3</v>
-      </c>
       <c r="K67" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
@@ -10316,17 +10200,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Rec_CookedMeat</t>
+          <t>Rec_Steel</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>구운 고기</t>
+          <t>강철 주괴</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Food_CookedMeat</t>
+          <t>Res_Steel</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -10334,28 +10218,28 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Food_RawMeat x1</t>
+          <t>Res_IronOre x3 + Res_Coal x2</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="G68" t="n">
+        <v>130</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>제련</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
         <v>12</v>
       </c>
-      <c r="H68" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>요리</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>6</v>
-      </c>
       <c r="K68" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
@@ -10367,17 +10251,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Rec_Bronze</t>
+          <t>Rec_SilverIngot</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>청동 주괴</t>
+          <t>은 주괴</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Res_Bronze</t>
+          <t>Res_SilverIngot</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -10385,17 +10269,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Res_CopperOre x3 + Res_TinOre x1 + Res_Coal x1</t>
+          <t>Res_SilverOre x3 + Res_Coal x1</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="G69" t="n">
-        <v>91</v>
+        <v>193</v>
       </c>
       <c r="H69" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -10403,10 +10287,10 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K69" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
@@ -10418,17 +10302,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Rec_Steel</t>
+          <t>Rec_GoldIngot</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>강철 주괴</t>
+          <t>금 주괴</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Res_Steel</t>
+          <t>Res_GoldIngot</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -10436,17 +10320,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Res_IronOre x3 + Res_Coal x2</t>
+          <t>Res_GoldOre x3 + Res_Coal x2</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="G70" t="n">
-        <v>130</v>
+        <v>326</v>
       </c>
       <c r="H70" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -10454,10 +10338,10 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K70" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
@@ -10466,111 +10350,9 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Rec_SilverIngot</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>은 주괴</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Res_SilverIngot</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Res_SilverOre x3 + Res_Coal x1</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>115</v>
-      </c>
-      <c r="G71" t="n">
-        <v>193</v>
-      </c>
-      <c r="H71" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>제련</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>18</v>
-      </c>
-      <c r="K71" t="n">
-        <v>40</v>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>SO</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Rec_GoldIngot</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>금 주괴</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Res_GoldIngot</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Res_GoldOre x3 + Res_Coal x2</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>185</v>
-      </c>
-      <c r="G72" t="n">
-        <v>326</v>
-      </c>
-      <c r="H72" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>제련</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>26</v>
-      </c>
-      <c r="K72" t="n">
-        <v>55</v>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>SO</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M72"/>
-  <conditionalFormatting sqref="H2:H72">
+  <autoFilter ref="A1:M70"/>
+  <conditionalFormatting sqref="H2:H70">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>1</formula>
     </cfRule>
@@ -10585,7 +10367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10661,22 +10443,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PrisonCage</t>
+          <t>CraftingTable_Labor</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>우리</t>
+          <t>작업대</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>가구</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10685,7 +10467,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -10694,39 +10476,43 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="K2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Grave</t>
+          <t>PrisonBed</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>무덤</t>
+          <t>죄수 침대</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>가구</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -10737,28 +10523,28 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pyre</t>
+          <t>CraftingTable_Stonecut</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>화장터</t>
+          <t>석재 가공대</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>가구</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -10767,39 +10553,47 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Res_Stonecutting</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>40</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FarmPlot</t>
+          <t>CraftingTable_Woodwork</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>밭</t>
+          <t>제재소</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10808,48 +10602,56 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Res_Woodworking</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>ButcherTable</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>물</t>
+          <t>도축대</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -10864,39 +10666,43 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TreeBuilding</t>
+          <t>CraftingTable_Smelt</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>나무 심기</t>
+          <t>용광로</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Res_Smelting</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>O</t>
@@ -10909,23 +10715,23 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>StoneBuilding</t>
+          <t>PrisonCage</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>돌</t>
+          <t>우리</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10935,55 +10741,63 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Node_CoalSeam</t>
+          <t>CraftingTable_Cook</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>석탄층</t>
+          <t>조리대</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Res_Cooking</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
@@ -10991,40 +10805,48 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Node_CopperVein</t>
+          <t>CraftingTable_Weapon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>구리 광맥</t>
+          <t>무기 제작대</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Res_WeaponSmithing</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
@@ -11032,40 +10854,44 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Node_TinVein</t>
+          <t>CraftingTable_Armor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>주석 광맥</t>
+          <t>방어구 제작대</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
@@ -11073,40 +10899,48 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Node_IronVein</t>
+          <t>CraftingTable_Alchemy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>철 광맥</t>
+          <t>연금술대</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_CutStone</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Res_Alchemy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
@@ -11114,40 +10948,44 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Node_SilverVein</t>
+          <t>CraftingTable_Gemcut</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>은 광맥</t>
+          <t>보석 연마대</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_CutStone</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
@@ -11155,40 +10993,44 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Node_GoldVein</t>
+          <t>ResearchTable</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>금 광맥</t>
+          <t>연구대</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
@@ -11196,23 +11038,23 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Node_MagicCrystal</t>
+          <t>Grave</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>마력석 결정</t>
+          <t>무덤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>가구</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11226,39 +11068,39 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>110</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Node_EtherCrystal</t>
+          <t>Pyre</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에테르석 결정</t>
+          <t>화장터</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>가구</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -11267,57 +11109,57 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>120</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Node_VoidCrystal</t>
+          <t>SubCore</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>공허석 결정</t>
+          <t>서브코어</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>가구</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_CutStone</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
         <v>130</v>
       </c>
@@ -11325,12 +11167,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Node_RubyVein</t>
+          <t>FarmPlot</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>루비 광맥</t>
+          <t>밭</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -11340,38 +11182,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>140</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Node_SapphireVein</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>사파이어 광맥</t>
+          <t>물</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11381,15 +11223,23 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2x1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Res_Stone</t>
+        </is>
+      </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
@@ -11397,18 +11247,18 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>141</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Node_TopazVein</t>
+          <t>TreeBuilding</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>토파즈 광맥</t>
+          <t>나무 심기</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11418,15 +11268,23 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2x1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Res_Wood</t>
+        </is>
+      </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
@@ -11434,18 +11292,18 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>142</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Node_EmeraldVein</t>
+          <t>StoneBuilding</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>에메랄드 광맥</t>
+          <t>돌</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11455,10 +11313,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2x1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Res_Stone</t>
+        </is>
+      </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
@@ -11471,28 +11333,28 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>143</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Node_CoalSeam</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>바닥</t>
+          <t>석탄층</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -11501,34 +11363,34 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Node_CopperVein</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>창고</t>
+          <t>구리 광맥</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -11538,18 +11400,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
@@ -11557,44 +11415,40 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LargeStorage</t>
+          <t>Node_TinVein</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>큰 창고</t>
+          <t>주석 광맥</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
@@ -11602,44 +11456,40 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CraftingTable_Labor</t>
+          <t>Node_IronVein</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>작업대</t>
+          <t>철 광맥</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
@@ -11647,105 +11497,105 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bed</t>
+          <t>Node_SilverVein</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>침대</t>
+          <t>은 광맥</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PrisonBed</t>
+          <t>Node_GoldVein</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>죄수 침대</t>
+          <t>금 광맥</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>31</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CraftingTable_Stonecut</t>
+          <t>Node_MagicCrystal</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>석재 가공대</t>
+          <t>마력석 결정</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -11759,18 +11609,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>35</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Res_Stonecutting</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
@@ -11778,23 +11620,23 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CraftingTable_Woodwork</t>
+          <t>Node_EtherCrystal</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>제재소</t>
+          <t>에테르석 결정</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -11804,22 +11646,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>30</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Res_Woodworking</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
@@ -11827,23 +11661,23 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ButcherTable</t>
+          <t>Node_VoidCrystal</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>도축대</t>
+          <t>공허석 결정</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -11853,18 +11687,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
@@ -11872,28 +11702,28 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CraftingTable_Smelt</t>
+          <t>Node_RubyVein</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>용광로</t>
+          <t>루비 광맥</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11902,18 +11732,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>40</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Res_Smelting</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
@@ -11921,23 +11743,23 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CraftingTable_Cook</t>
+          <t>Node_SapphireVein</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>조리대</t>
+          <t>사파이어 광맥</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -11947,22 +11769,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Sapphire</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Res_Cooking</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
@@ -11970,23 +11784,23 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>70</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CraftingTable_Weapon</t>
+          <t>Node_TopazVein</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>무기 제작대</t>
+          <t>토파즈 광맥</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -11996,22 +11810,14 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Topaz</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>25</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Res_WeaponSmithing</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
@@ -12019,23 +11825,23 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CraftingTable_Armor</t>
+          <t>Node_EmeraldVein</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>방어구 제작대</t>
+          <t>에메랄드 광맥</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>건물</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -12045,18 +11851,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Emerald</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>25</v>
       </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
@@ -12064,43 +11866,39 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>90</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CraftingTable_Alchemy</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>연금술대</t>
+          <t>창고</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>바닥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Res_CutStone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>20</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Res_Alchemy</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>O</t>
@@ -12113,37 +11911,37 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CraftingTable_Gemcut</t>
+          <t>LargeStorage</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>보석 연마대</t>
+          <t>큰 창고</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>바닥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Res_CutStone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
@@ -12158,63 +11956,59 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>110</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ResearchTable</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>연구대</t>
+          <t>바닥</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>방어</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SubCore</t>
+          <t>Bed</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>서브코어</t>
+          <t>침대</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -12224,16 +12018,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Res_CutStone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
@@ -12244,37 +12038,37 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Barricade</t>
+          <t>Campfire</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>나무 바리케이드</t>
+          <t>화톳불</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>보관</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Res_Wood</t>
+          <t>Res_Stone</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
@@ -12289,18 +12083,18 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Palisade</t>
+          <t>Barricade</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>목책</t>
+          <t>나무 바리케이드</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12310,7 +12104,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -12319,7 +12113,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
@@ -12334,18 +12128,18 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Palisade</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>벽</t>
+          <t>목책</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -12360,11 +12154,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Res_Stone</t>
+          <t>Res_Wood</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
@@ -12379,11 +12173,56 @@
         </is>
       </c>
       <c r="K41" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>벽</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Res_Stone</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13217,7 +13056,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>암흑마법 +7 · 인지력 +5 · 사교 -4</t>
+          <t>암흑 마법 +7 · 인지력 +5 · 사교 -4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -13253,7 +13092,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>강인함 +8 · 암흑마법 +6 · 사교 -8</t>
+          <t>강인함 +8 · 암흑 마법 +6 · 사교 -8</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -13289,7 +13128,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>암흑마법 +8 · 강인함 +5 · 원예 -5</t>
+          <t>암흑 마법 +8 · 강인함 +5 · 원예 -5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -13873,7 +13712,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>암흑마법 +12 · 인지력 +6 · 사교 -8</t>
+          <t>암흑 마법 +12 · 인지력 +6 · 사교 -8</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -13945,7 +13784,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>암흑마법 +10 · 연구 +8 · 근력 -5</t>
+          <t>암흑 마법 +10 · 연구 +8 · 근력 -5</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -14116,7 +13955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14294,11 +14133,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Resource, Defense, Building, Misc</t>
+          <t>Resource, Defense, Living, Misc, Floor, Storage, Production, Prison</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -14390,27 +14229,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DamageCategory</t>
+          <t>DamageType</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Physical, Elemental, Dark, Holy</t>
+          <t>Slash, Pierce, Blunt, Fire, Water, Earth, Lightning, Arcane, Dark, Holy</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Combat/DamageCategory.cs</t>
+          <t>Assets/1_Script/Combat/DamageType.cs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DamageElement</t>
+          <t>EscortDest</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -14418,39 +14257,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None, Fire, Ice, Lightning, Poison</t>
+          <t>None, Cage, Bed, Grave, Pyre</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Combat/DamageElement.cs</t>
+          <t>Assets/1_Script/unit/PrisonEscort.cs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EscortDest</t>
+          <t>FactionStance</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None, Cage, Bed, Grave, Pyre</t>
+          <t>Ally, Neutral, Hostile</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/PrisonEscort.cs</t>
+          <t>Assets/1_Script/unit/FactionData.cs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FactionStance</t>
+          <t>FarmState</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -14458,119 +14297,119 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ally, Neutral, Hostile</t>
+          <t>Empty, Planted, ReadyToHarvest</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/FactionData.cs</t>
+          <t>Assets/1_Script/Job/FarmPlot.cs</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FarmState</t>
+          <t>GameEventType</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Empty, Planted, ReadyToHarvest</t>
+          <t>Raid, Merchant, Reinforcement, Discovery</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/FarmPlot.cs</t>
+          <t>Assets/1_Script/Event/GameEventType.cs</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GameEventType</t>
+          <t>GameMode</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raid, Merchant, Reinforcement, Discovery</t>
+          <t>Field, World</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Event/GameEventType.cs</t>
+          <t>Assets/1_Script/World/GameMode.cs</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GameMode</t>
+          <t>ItemQuality</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Field, World</t>
+          <t>Common, Uncommon, Rare, Unique, Epic, Legendary</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Assets/1_Script/World/GameMode.cs</t>
+          <t>Assets/1_Script/Item/ItemQuality.cs</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ItemQuality</t>
+          <t>JobCategory</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Common, Uncommon, Rare, Unique, Epic, Legendary</t>
+          <t>None, Mining, Hauling, Farming, Logging, Construction, Guard, Crafting, Research, Unload, Medical, Warden, Butcher</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/ItemQuality.cs</t>
+          <t>Assets/1_Script/Job/JobCategory.cs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JobCategory</t>
+          <t>JobStatus</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None, Mining, Hauling, Farming, Logging, Construction, Guard, Crafting, Research, Unload, Medical, Warden, Butcher</t>
+          <t>Available, Reserved, InProgress, Done, Cancelled</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/JobCategory.cs</t>
+          <t>Assets/1_Script/Job/JobBase.cs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JobStatus</t>
+          <t>MerchantType</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -14578,32 +14417,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Available, Reserved, InProgress, Done, Cancelled</t>
+          <t>General, Weapon, Armor, Material, Food</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/JobBase.cs</t>
+          <t>Assets/1_Script/Event/MerchantData.cs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MerchantType</t>
+          <t>NeedKind</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>General, Weapon, Armor, Material, Food</t>
+          <t>Hunger, Rest</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Event/MerchantData.cs</t>
+          <t>Assets/1_Script/unit/Needs.cs</t>
         </is>
       </c>
     </row>
@@ -14650,27 +14489,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PhysicalType</t>
+          <t>PlacementMode</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slash, Pierce, Blunt</t>
+          <t>Grid, Free</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Combat/PhysicalType.cs</t>
+          <t>Assets/1_Script/BuildModeManager.cs</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PlacementMode</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -14678,107 +14517,107 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Grid, Free</t>
+          <t>Forever, Count</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Assets/1_Script/BuildModeManager.cs</t>
+          <t>Assets/1_Script/Job/ButcherBill.cs</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Repeat</t>
+          <t>ResourceGroup</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Forever, Count</t>
+          <t>Stone, Ore, Gem, Ingot, Wood, Currency</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/ButcherBill.cs</t>
+          <t>Assets/1_Script/Item/ResourceGroup.cs</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ResourceGroup</t>
+          <t>Ripeness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stone, Ore, Gem, Ingot, Wood, Currency</t>
+          <t>FreshOnly, NotBones, Any</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/ResourceGroup.cs</t>
+          <t>Assets/1_Script/Job/ButcherBill.cs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ripeness</t>
+          <t>SlotKind</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FreshOnly, NotBones, Any</t>
+          <t>MainHand, OffHand, Head, Chest, Hands, Legs</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/ButcherBill.cs</t>
+          <t>Assets/1_Script/UI/EquipSlotUI.cs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SlotKind</t>
+          <t>StatGrade</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MainHand, OffHand, Head, Chest, Hands, Legs</t>
+          <t>FMinus, F, FPlus, EMinus, E, EPlus, DMinus, D, DPlus, CMinus, C, CPlus, BMinus, B, BPlus, AMinus, A, APlus, SMinus, S, SPlus, SSMinus, SS, SSPlus, SSSMinus, SSS, SSSPlus</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Assets/1_Script/UI/EquipSlotUI.cs</t>
+          <t>Assets/1_Script/unit/StatGrade.cs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>StatGrade</t>
+          <t>StatName</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FMinus, F, FPlus, EMinus, E, EPlus, DMinus, D, DPlus, CMinus, C, CPlus, BMinus, B, BPlus, AMinus, A, APlus, SMinus, S, SPlus, SSMinus, SS, SSPlus, SSSMinus, SSS, SSSPlus</t>
+          <t>Strength, Toughness, Dexterity, Cognition, MeleeAttack, MeleeDefense, RangedDefense, PrecisionShooting, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, FireMagic, WaterMagic, EarthMagic, LightningMagic, ArcaneMagic, DarkMagic, HolyMagic, MartialArts, Evasion, Athletics, Swimming, Labor, Mining, Growing, Cutting, Taming, Cooking, Medicine, Research, WeaponCrafting, ArmorCrafting, Alchemy, Smelting, Stonecutting, Woodworking, Gemcutting, Social, Shield</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -14790,47 +14629,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>StatName</t>
+          <t>StatusEffectType</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Strength, Toughness, Dexterity, Cognition, MeleeAttack, MeleeDefense, RangedDefense, PrecisionShooting, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalMagic, DarkMagic, HolyMagic, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison, MartialArts, Evasion, Athletics, Swimming, Labor, Mining, Growing, Cutting, Taming, Cooking, Medicine, Research, WeaponCrafting, ArmorCrafting, Alchemy, Smelting, Stonecutting, Woodworking, Gemcutting, Social</t>
+          <t>Burning, HealReduction, Slowed, Weakened, Shielded, Hasted, Wet</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/StatGrade.cs</t>
+          <t>Assets/1_Script/unit/StatusEffectType.cs</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>StatusEffectType</t>
+          <t>StockView</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Burning, HealReduction, Slowed, Weakened, Shielded, Hasted</t>
+          <t>Cells, Cards</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Assets/1_Script/unit/StatusEffectType.cs</t>
+          <t>Assets/1_Script/UI/MerchantUI.cs</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>StockView</t>
+          <t>TileType</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -14838,79 +14677,79 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cells, Cards</t>
+          <t>Impassable, Passable</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Assets/1_Script/UI/MerchantUI.cs</t>
+          <t>Assets/1_Script/Map/TileData.cs</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TileType</t>
+          <t>TimePhase</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Impassable, Passable</t>
+          <t>Dawn, Morning, Day, Evening, Night</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Map/TileData.cs</t>
+          <t>Assets/1_Script/GameTimeManager.cs</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TimePhase</t>
+          <t>WeaponType</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dawn, Morning, Day, Evening, Night</t>
+          <t>Unarmed, Shield, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, Staff</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Assets/1_Script/GameTimeManager.cs</t>
+          <t>Assets/1_Script/Item/WeaponType.cs</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WeaponType</t>
+          <t>Whom</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Unarmed, Shield, OneHandSword, OneHandAxe, OneHandMace, TwoHandSword, TwoHandAxe, TwoHandMace, Polearm, Bow, Crossbow, Javelin, ElementalFire, ElementalIce, ElementalLightning, ElementalPoison, DarkFire, DarkIce, DarkLightning, DarkPoison, HolyFire, HolyIce, HolyLightning, HolyPoison</t>
+          <t>Hostile, NotAllied, Everyone</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Item/WeaponType.cs</t>
+          <t>Assets/1_Script/Job/ButcherBill.cs</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Whom</t>
+          <t>WorldBandBehavior</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -14918,57 +14757,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hostile, NotAllied, Everyone</t>
+          <t>Roam, Caravan, Patrol</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Assets/1_Script/Job/ButcherBill.cs</t>
+          <t>Assets/1_Script/World/WorldBandData.cs</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WorldBandBehavior</t>
+          <t>WorldNodeContent</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Roam, Caravan, Patrol</t>
+          <t>Empty, MySettlement, Town, EnemyLair, ResourceSite, Outpost</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Assets/1_Script/World/WorldBandData.cs</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>WorldNodeContent</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>6</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Empty, MySettlement, Town, EnemyLair, ResourceSite, Outpost</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
           <t>Assets/1_Script/World/WorldMap.cs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D42"/>
+  <autoFilter ref="A1:D41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>